--- a/shopping_list.xlsx
+++ b/shopping_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtsen\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtsen\Desktop\Claude\price-comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935887CC-A7D3-4ADA-BB80-77D04ADFF575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5803BBB5-3332-452E-8895-A845617E4258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4912772E-7773-4768-9AE2-362B9F355871}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="48" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="437">
   <si>
     <t>Unit price</t>
   </si>
@@ -980,6 +980,378 @@
   </si>
   <si>
     <t>Count of Item</t>
+  </si>
+  <si>
+    <t>Balconi Mix Max Cake Cocoa 350g</t>
+  </si>
+  <si>
+    <t>Woolworths Wholegrain Wrap 8Pk</t>
+  </si>
+  <si>
+    <t>Woolworths Mild Salsa</t>
+  </si>
+  <si>
+    <t>Sam's Pantry Granola Pink Lady Apple &amp; Cinnamon</t>
+  </si>
+  <si>
+    <t>Woolworths Black Beans</t>
+  </si>
+  <si>
+    <t>Woolworths Cous Cous</t>
+  </si>
+  <si>
+    <t>Woolworths Diced Italian Tomatoes</t>
+  </si>
+  <si>
+    <t>Woolworths Tuna In Springwater</t>
+  </si>
+  <si>
+    <t>Woolworths 12 Extra Large Free Range Eggs</t>
+  </si>
+  <si>
+    <t>Aero Peppermint Milk Chocolate Block</t>
+  </si>
+  <si>
+    <t>KitKat Milk Chocolate Mini Bars Share Pack</t>
+  </si>
+  <si>
+    <t>Snickers Milk Chocolate Party Share Bag</t>
+  </si>
+  <si>
+    <t>Woolworths Extra Virgin Spanish Olive Oil</t>
+  </si>
+  <si>
+    <t>Mainland Tasty Cheese Block Cheese</t>
+  </si>
+  <si>
+    <t>Woolworths Natural Greek Style Yoghurt</t>
+  </si>
+  <si>
+    <t>Woolworths Thickened Cream</t>
+  </si>
+  <si>
+    <t>Woolworths Whole Milk Full Cream Milk</t>
+  </si>
+  <si>
+    <t>Woolworths 100% Canadian Maple Syrup</t>
+  </si>
+  <si>
+    <t>Woolworths Peppermint Tea</t>
+  </si>
+  <si>
+    <t>Eat Now Hass Avocado</t>
+  </si>
+  <si>
+    <t>Parsnip Fresh</t>
+  </si>
+  <si>
+    <t>Woolworths Baby Leaf Spinach</t>
+  </si>
+  <si>
+    <t>Woolworths Broccolini Bunch</t>
+  </si>
+  <si>
+    <t>Woolworths Cherry Tomatoes Punnet</t>
+  </si>
+  <si>
+    <t>Woolworths Corn Sweet</t>
+  </si>
+  <si>
+    <t>Woolworths Cos Hearts Lettuce</t>
+  </si>
+  <si>
+    <t>Woolworths Dill Fresh Herb</t>
+  </si>
+  <si>
+    <t>Woolworths Garlic Heads CLOVE</t>
+  </si>
+  <si>
+    <t>Woolworths Onion Brown Bag</t>
+  </si>
+  <si>
+    <t>Woolworths Red Onions Bag</t>
+  </si>
+  <si>
+    <t>Woolworths Red Washed Potatoes Bag</t>
+  </si>
+  <si>
+    <t>Ajax Spray &amp; Wipe Bathroom Cleaner Trigger</t>
+  </si>
+  <si>
+    <t>Nutella Hazelnut Chocolate Spread Spread</t>
+  </si>
+  <si>
+    <t>Woolworths BBQ Australian Lamb Koftas Honey &amp; Mint</t>
+  </si>
+  <si>
+    <t>Woolworths Beef Porterhouse Steak &amp; Butter</t>
+  </si>
+  <si>
+    <t>Woolworths Lean Beef Mince</t>
+  </si>
+  <si>
+    <t>Woolworths Pork &amp; Veal Meatballs</t>
+  </si>
+  <si>
+    <t>Woolworths RSPCA Approved Chicken Thigh Skinless Cutlets Bone-In</t>
+  </si>
+  <si>
+    <t>Strike 2 Ply Paper Towel 2 Ply</t>
+  </si>
+  <si>
+    <t>Maggi 2 Minute Chicken Flavour Instant Noodles</t>
+  </si>
+  <si>
+    <t>Woolworths Pasta Spaghetti</t>
+  </si>
+  <si>
+    <t>Basa Thawed Freshwater Basa Fillets</t>
+  </si>
+  <si>
+    <t>Woolworths RSPCA Approved Chicken Breast Fillet</t>
+  </si>
+  <si>
+    <t>Vevelle White 2 Ply Toilet Tissue</t>
+  </si>
+  <si>
+    <t>McVitie's Digestives Choc Tops Milk Chocolate</t>
+  </si>
+  <si>
+    <t>Magnum Almond Ice Cream Sticks</t>
+  </si>
+  <si>
+    <t>Celery Fresh Whole</t>
+  </si>
+  <si>
+    <t>Woolworths Capsicum Green</t>
+  </si>
+  <si>
+    <t>Woolworths Beef Family Roast</t>
+  </si>
+  <si>
+    <t>Woolworths Cook Chicken Roasting Portions Italian Style</t>
+  </si>
+  <si>
+    <t>Woolworths Salmon Portions Skin On</t>
+  </si>
+  <si>
+    <t>Continental Classics Cup A Soup Chicken With Lots Of Noodles</t>
+  </si>
+  <si>
+    <t>Providore Premium Tomato Paste Triple Concentrate</t>
+  </si>
+  <si>
+    <t>Vegeta Chicken Stock Powder</t>
+  </si>
+  <si>
+    <t>Fresh Eggplant</t>
+  </si>
+  <si>
+    <t>Mushrooms Flat Large Loose</t>
+  </si>
+  <si>
+    <t>Woolworths Beef Chuck Steak Medium</t>
+  </si>
+  <si>
+    <t>Woolworths Arborio Risotto Rice</t>
+  </si>
+  <si>
+    <t>Little One's Size 5 Ultra Dry Nappies Walker 12-17kg Boys &amp; Girls</t>
+  </si>
+  <si>
+    <t>Woolworths Sour Cream</t>
+  </si>
+  <si>
+    <t>Woolworths Garlic Chicken Bites</t>
+  </si>
+  <si>
+    <t>Woolworths Potato Minis</t>
+  </si>
+  <si>
+    <t>Woolworths Fresh Tasmanian Atlantic Skin On Salmon Fillets</t>
+  </si>
+  <si>
+    <t>Huggies Ultra Dry Nappies Boys Size 5 (13-18kg)</t>
+  </si>
+  <si>
+    <t>Sam's Pantry Granola Maple &amp; Pecan</t>
+  </si>
+  <si>
+    <t>Woolworths Baby Corn Spears</t>
+  </si>
+  <si>
+    <t>Woolworths Baked Beans In Tomato Sauce</t>
+  </si>
+  <si>
+    <t>Woolworths Chickpeas</t>
+  </si>
+  <si>
+    <t>Woolworths Extra Virgin Olive Oil Spray</t>
+  </si>
+  <si>
+    <t>Woolworths Fresh Continental Parsley Bunch</t>
+  </si>
+  <si>
+    <t>Woolworths Red Watermelon Cut Quarter</t>
+  </si>
+  <si>
+    <t>Woolworths Washed Potato Bag</t>
+  </si>
+  <si>
+    <t>Help@Hand Cotton Tips No Plastic Stems</t>
+  </si>
+  <si>
+    <t>Woolworths Basmati Rice</t>
+  </si>
+  <si>
+    <t>Just Caught Cooked Prawns Tail Off Extra Small</t>
+  </si>
+  <si>
+    <t>Ingham's Turkey Breast Shaved From The Deli</t>
+  </si>
+  <si>
+    <t>Head &amp; Shoulders Clean &amp; Balanced Anti Dandruff Shampoo</t>
+  </si>
+  <si>
+    <t>Rexona Men 48hr Deodorant Stick Sport Defence</t>
+  </si>
+  <si>
+    <t>Kettle Ridge Cut Potato Chips Salt &amp; Vinegar</t>
+  </si>
+  <si>
+    <t>Continental Classics Cup A Soup Creamy Chicken With Croutons</t>
+  </si>
+  <si>
+    <t>Continental Classics Cup A Soup Italian Minestrone With Pasta</t>
+  </si>
+  <si>
+    <t>Continental Cup A Soup Hearty Pea &amp; Ham</t>
+  </si>
+  <si>
+    <t>Maltesers Milk Chocolate Party Gift Box</t>
+  </si>
+  <si>
+    <t>La Gina Extra Virgin Olive Oil</t>
+  </si>
+  <si>
+    <t>Olsson's Rock Sea Salt</t>
+  </si>
+  <si>
+    <t>Thomas Dux Vintage Cheddar</t>
+  </si>
+  <si>
+    <t>Woolworths Cheese Burger Slices</t>
+  </si>
+  <si>
+    <t>Schweppes Lemon Lime Bitters Soft Drink Mixer Bottle</t>
+  </si>
+  <si>
+    <t>Woolworths Spring Water Bottles</t>
+  </si>
+  <si>
+    <t>Woolworths Ice Cream Cones Vanilla</t>
+  </si>
+  <si>
+    <t>Woolworths Washed Potatoes Bag</t>
+  </si>
+  <si>
+    <t>Osem Snacks Bamba With Peanuts</t>
+  </si>
+  <si>
+    <t>Gillette Shaving Foam Sensitive Skin Value Pack</t>
+  </si>
+  <si>
+    <t>Obela Hommus Dip With Garlic Smashed Falafel</t>
+  </si>
+  <si>
+    <t>Vegeta Chicken Stock Cubes</t>
+  </si>
+  <si>
+    <t>Woolworths Rosemary Leaves</t>
+  </si>
+  <si>
+    <t>Woolworths Thyme Leaves</t>
+  </si>
+  <si>
+    <t>Schweppes Zero Sugar Mixers Lemon Lime &amp; Bitters Soft Drink Bottle</t>
+  </si>
+  <si>
+    <t>Woolworths 4 Angus Quarter Pound Beef Burgers</t>
+  </si>
+  <si>
+    <t>Fresh Medjool Dates Loose</t>
+  </si>
+  <si>
+    <t>Arnott's Tim Tam Double Chocolate Biscuits</t>
+  </si>
+  <si>
+    <t>M&amp;M's Milk Chocolate Snack &amp; Share Bag</t>
+  </si>
+  <si>
+    <t>M&amp;M's Peanut Milk Chocolate Snack &amp; Share Bag</t>
+  </si>
+  <si>
+    <t>Woolworths RSPCA Approved Chicken Drumsticks</t>
+  </si>
+  <si>
+    <t>Maltesers Milk Chocolate Snack &amp; Share Party Bag</t>
+  </si>
+  <si>
+    <t>The Organic Milk Co. Organic Shredded Mozzarella</t>
+  </si>
+  <si>
+    <t>Peters Drumstick Minis Ice Cream Vanilla</t>
+  </si>
+  <si>
+    <t>Woolworths Pesto Basil</t>
+  </si>
+  <si>
+    <t>Essentials Tuna In Oil</t>
+  </si>
+  <si>
+    <t>Obela Everyday Smooth Classic Hommus</t>
+  </si>
+  <si>
+    <t>Woolworths Full Cream Milk</t>
+  </si>
+  <si>
+    <t>Woolworths Celery Heart</t>
+  </si>
+  <si>
+    <t>Ingham's Oven Roasted Turkey Breast Sliced From The Deli</t>
+  </si>
+  <si>
+    <t>Help@Hand Cotton Balls</t>
+  </si>
+  <si>
+    <t>Cadbury Dairy Milk Large Top Deck Chocolate Block</t>
+  </si>
+  <si>
+    <t>Woolworths Mixed Herbs Dried</t>
+  </si>
+  <si>
+    <t>Woolworths Oregano Leaves</t>
+  </si>
+  <si>
+    <t>Woolworths Greek Style Yoghurt</t>
+  </si>
+  <si>
+    <t>Bulla Mini Frozen Yoghurt Assorted Flavours</t>
+  </si>
+  <si>
+    <t>Woolworths Asparagus Mini</t>
+  </si>
+  <si>
+    <t>Woolworths Green Cabbage Quarter</t>
+  </si>
+  <si>
+    <t>Domestos Disinfectant Bleach Regular</t>
+  </si>
+  <si>
+    <t>Woolworths Essentials Microfibre Cloth</t>
+  </si>
+  <si>
+    <t>Armada Resealable Sandwich Bag</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1032,7 +1404,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8506,7 +8877,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F5F0204-D1ED-43ED-B33E-E318E737D7D3}" name="PivotTable2" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4F5F0204-D1ED-43ED-B33E-E318E737D7D3}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
@@ -9205,7 +9576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFCB0D3-CD91-42A0-AF12-5AA480AF2E6C}">
-  <dimension ref="A1:E1014"/>
+  <dimension ref="A1:E1458"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.36328125" bestFit="1" customWidth="1"/>
@@ -26448,6 +26819,7554 @@
       </c>
       <c r="E1014" s="1">
         <v>45864</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1015" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1015">
+        <v>3.85</v>
+      </c>
+      <c r="C1015">
+        <v>1</v>
+      </c>
+      <c r="D1015">
+        <v>3.85</v>
+      </c>
+      <c r="E1015" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1016" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1016">
+        <v>7.7</v>
+      </c>
+      <c r="C1016">
+        <v>2</v>
+      </c>
+      <c r="D1016">
+        <v>15.4</v>
+      </c>
+      <c r="E1016" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1017" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1017">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1017">
+        <v>2</v>
+      </c>
+      <c r="D1017">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E1017" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1018" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1018">
+        <v>12.5</v>
+      </c>
+      <c r="C1018">
+        <v>1</v>
+      </c>
+      <c r="D1018">
+        <v>12.5</v>
+      </c>
+      <c r="E1018" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1019" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1019">
+        <v>8.5</v>
+      </c>
+      <c r="C1019">
+        <v>1</v>
+      </c>
+      <c r="D1019">
+        <v>8.5</v>
+      </c>
+      <c r="E1019" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1020" t="s">
+        <v>315</v>
+      </c>
+      <c r="B1020">
+        <v>1.9</v>
+      </c>
+      <c r="C1020">
+        <v>2</v>
+      </c>
+      <c r="D1020">
+        <v>3.8</v>
+      </c>
+      <c r="E1020" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1021" t="s">
+        <v>316</v>
+      </c>
+      <c r="B1021">
+        <v>7.6</v>
+      </c>
+      <c r="C1021">
+        <v>1</v>
+      </c>
+      <c r="D1021">
+        <v>7.6</v>
+      </c>
+      <c r="E1021" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1022" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1022">
+        <v>1.6</v>
+      </c>
+      <c r="C1022">
+        <v>1</v>
+      </c>
+      <c r="D1022">
+        <v>1.6</v>
+      </c>
+      <c r="E1022" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1023" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1023">
+        <v>4.8</v>
+      </c>
+      <c r="C1023">
+        <v>1</v>
+      </c>
+      <c r="D1023">
+        <v>4.8</v>
+      </c>
+      <c r="E1023" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1024" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1024">
+        <v>1</v>
+      </c>
+      <c r="C1024">
+        <v>1</v>
+      </c>
+      <c r="D1024">
+        <v>1</v>
+      </c>
+      <c r="E1024" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1025" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1025">
+        <v>2</v>
+      </c>
+      <c r="C1025">
+        <v>1</v>
+      </c>
+      <c r="D1025">
+        <v>2</v>
+      </c>
+      <c r="E1025" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1026" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1026">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1026">
+        <v>2</v>
+      </c>
+      <c r="D1026">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E1026" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1027" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1027">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1027">
+        <v>3</v>
+      </c>
+      <c r="D1027">
+        <v>3.3</v>
+      </c>
+      <c r="E1027" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1028" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1028">
+        <v>6.5</v>
+      </c>
+      <c r="C1028">
+        <v>1</v>
+      </c>
+      <c r="D1028">
+        <v>6.5</v>
+      </c>
+      <c r="E1028" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1029" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1029">
+        <v>3.75</v>
+      </c>
+      <c r="C1029">
+        <v>2</v>
+      </c>
+      <c r="D1029">
+        <v>7.5</v>
+      </c>
+      <c r="E1029" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1030" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1030">
+        <v>8</v>
+      </c>
+      <c r="C1030">
+        <v>1</v>
+      </c>
+      <c r="D1030">
+        <v>8</v>
+      </c>
+      <c r="E1030" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1031" t="s">
+        <v>322</v>
+      </c>
+      <c r="B1031">
+        <v>7.5</v>
+      </c>
+      <c r="C1031">
+        <v>2</v>
+      </c>
+      <c r="D1031">
+        <v>13</v>
+      </c>
+      <c r="E1031" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1032" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1032">
+        <v>5.25</v>
+      </c>
+      <c r="C1032">
+        <v>2</v>
+      </c>
+      <c r="D1032">
+        <v>10.5</v>
+      </c>
+      <c r="E1032" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1033" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1033">
+        <v>8</v>
+      </c>
+      <c r="C1033">
+        <v>1</v>
+      </c>
+      <c r="D1033">
+        <v>8</v>
+      </c>
+      <c r="E1033" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1034" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1034">
+        <v>2.4</v>
+      </c>
+      <c r="C1034">
+        <v>2</v>
+      </c>
+      <c r="D1034">
+        <v>4.8</v>
+      </c>
+      <c r="E1034" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1035" t="s">
+        <v>325</v>
+      </c>
+      <c r="B1035">
+        <v>14</v>
+      </c>
+      <c r="C1035">
+        <v>1</v>
+      </c>
+      <c r="D1035">
+        <v>14</v>
+      </c>
+      <c r="E1035" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1036" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1036">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="C1036">
+        <v>1</v>
+      </c>
+      <c r="D1036">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E1036" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1037" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1037">
+        <v>11</v>
+      </c>
+      <c r="C1037">
+        <v>1</v>
+      </c>
+      <c r="D1037">
+        <v>11</v>
+      </c>
+      <c r="E1037" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1038" t="s">
+        <v>234</v>
+      </c>
+      <c r="B1038">
+        <v>5.7</v>
+      </c>
+      <c r="C1038">
+        <v>1</v>
+      </c>
+      <c r="D1038">
+        <v>5.7</v>
+      </c>
+      <c r="E1038" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1039" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1039">
+        <v>3.8</v>
+      </c>
+      <c r="C1039">
+        <v>1</v>
+      </c>
+      <c r="D1039">
+        <v>3.8</v>
+      </c>
+      <c r="E1039" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1040" t="s">
+        <v>328</v>
+      </c>
+      <c r="B1040">
+        <v>3.4</v>
+      </c>
+      <c r="C1040">
+        <v>2</v>
+      </c>
+      <c r="D1040">
+        <v>6.8</v>
+      </c>
+      <c r="E1040" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1041" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1041">
+        <v>5.15</v>
+      </c>
+      <c r="C1041">
+        <v>2</v>
+      </c>
+      <c r="D1041">
+        <v>10.3</v>
+      </c>
+      <c r="E1041" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1042" t="s">
+        <v>330</v>
+      </c>
+      <c r="B1042">
+        <v>6</v>
+      </c>
+      <c r="C1042">
+        <v>1</v>
+      </c>
+      <c r="D1042">
+        <v>6</v>
+      </c>
+      <c r="E1042" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1043" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1043">
+        <v>2.95</v>
+      </c>
+      <c r="C1043">
+        <v>3</v>
+      </c>
+      <c r="D1043">
+        <v>8.85</v>
+      </c>
+      <c r="E1043" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1044" t="s">
+        <v>331</v>
+      </c>
+      <c r="B1044">
+        <v>1.75</v>
+      </c>
+      <c r="C1044">
+        <v>1</v>
+      </c>
+      <c r="D1044">
+        <v>1.75</v>
+      </c>
+      <c r="E1044" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1045" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1045">
+        <v>0.72</v>
+      </c>
+      <c r="C1045">
+        <v>4</v>
+      </c>
+      <c r="D1045">
+        <v>2.88</v>
+      </c>
+      <c r="E1045" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1046" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1046">
+        <v>4.5</v>
+      </c>
+      <c r="C1046">
+        <v>1</v>
+      </c>
+      <c r="D1046">
+        <v>4.5</v>
+      </c>
+      <c r="E1046" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1047" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1047">
+        <v>2</v>
+      </c>
+      <c r="C1047">
+        <v>2</v>
+      </c>
+      <c r="D1047">
+        <v>4</v>
+      </c>
+      <c r="E1047" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1048" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1048">
+        <v>1.49</v>
+      </c>
+      <c r="C1048">
+        <v>2</v>
+      </c>
+      <c r="D1048">
+        <v>2.98</v>
+      </c>
+      <c r="E1048" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1049" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1049">
+        <v>2.95</v>
+      </c>
+      <c r="C1049">
+        <v>1</v>
+      </c>
+      <c r="D1049">
+        <v>2.95</v>
+      </c>
+      <c r="E1049" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1050" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1050">
+        <v>3.9</v>
+      </c>
+      <c r="C1050">
+        <v>1</v>
+      </c>
+      <c r="D1050">
+        <v>3.9</v>
+      </c>
+      <c r="E1050" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1051" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1051">
+        <v>1.42</v>
+      </c>
+      <c r="C1051">
+        <v>2</v>
+      </c>
+      <c r="D1051">
+        <v>2.84</v>
+      </c>
+      <c r="E1051" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1052" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1052">
+        <v>12.9</v>
+      </c>
+      <c r="C1052">
+        <v>0.6</v>
+      </c>
+      <c r="D1052">
+        <v>7.74</v>
+      </c>
+      <c r="E1052" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1053" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1053">
+        <v>1.75</v>
+      </c>
+      <c r="C1053">
+        <v>1</v>
+      </c>
+      <c r="D1053">
+        <v>1.75</v>
+      </c>
+      <c r="E1053" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1054" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1054">
+        <v>2.5</v>
+      </c>
+      <c r="C1054">
+        <v>1</v>
+      </c>
+      <c r="D1054">
+        <v>2.5</v>
+      </c>
+      <c r="E1054" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1055" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1055">
+        <v>2.4</v>
+      </c>
+      <c r="C1055">
+        <v>1</v>
+      </c>
+      <c r="D1055">
+        <v>2.4</v>
+      </c>
+      <c r="E1055" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1056" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1056">
+        <v>3.8</v>
+      </c>
+      <c r="C1056">
+        <v>1</v>
+      </c>
+      <c r="D1056">
+        <v>3.8</v>
+      </c>
+      <c r="E1056" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1057" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1057">
+        <v>2.8</v>
+      </c>
+      <c r="C1057">
+        <v>1</v>
+      </c>
+      <c r="D1057">
+        <v>2.8</v>
+      </c>
+      <c r="E1057" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1058" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1058">
+        <v>2.9</v>
+      </c>
+      <c r="C1058">
+        <v>1</v>
+      </c>
+      <c r="D1058">
+        <v>2.9</v>
+      </c>
+      <c r="E1058" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1059" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1059">
+        <v>1.39</v>
+      </c>
+      <c r="C1059">
+        <v>8</v>
+      </c>
+      <c r="D1059">
+        <v>11.12</v>
+      </c>
+      <c r="E1059" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1060" t="s">
+        <v>334</v>
+      </c>
+      <c r="B1060">
+        <v>2.7</v>
+      </c>
+      <c r="C1060">
+        <v>1</v>
+      </c>
+      <c r="D1060">
+        <v>2.7</v>
+      </c>
+      <c r="E1060" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1061" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1061">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C1061">
+        <v>1</v>
+      </c>
+      <c r="D1061">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E1061" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1062" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1062">
+        <v>3</v>
+      </c>
+      <c r="C1062">
+        <v>2</v>
+      </c>
+      <c r="D1062">
+        <v>6</v>
+      </c>
+      <c r="E1062" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1063" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1063">
+        <v>4.5</v>
+      </c>
+      <c r="C1063">
+        <v>1</v>
+      </c>
+      <c r="D1063">
+        <v>4.5</v>
+      </c>
+      <c r="E1063" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1064" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1064">
+        <v>2.5</v>
+      </c>
+      <c r="C1064">
+        <v>1</v>
+      </c>
+      <c r="D1064">
+        <v>2.5</v>
+      </c>
+      <c r="E1064" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1065" t="s">
+        <v>339</v>
+      </c>
+      <c r="B1065">
+        <v>3.2</v>
+      </c>
+      <c r="C1065">
+        <v>1</v>
+      </c>
+      <c r="D1065">
+        <v>3.2</v>
+      </c>
+      <c r="E1065" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1066" t="s">
+        <v>340</v>
+      </c>
+      <c r="B1066">
+        <v>3.5</v>
+      </c>
+      <c r="C1066">
+        <v>1</v>
+      </c>
+      <c r="D1066">
+        <v>3.5</v>
+      </c>
+      <c r="E1066" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1067" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1067">
+        <v>2.5</v>
+      </c>
+      <c r="C1067">
+        <v>1</v>
+      </c>
+      <c r="D1067">
+        <v>2.5</v>
+      </c>
+      <c r="E1067" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1068" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1068">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C1068">
+        <v>1</v>
+      </c>
+      <c r="D1068">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E1068" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1069" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1069">
+        <v>6</v>
+      </c>
+      <c r="C1069">
+        <v>2</v>
+      </c>
+      <c r="D1069">
+        <v>12</v>
+      </c>
+      <c r="E1069" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1070" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1070">
+        <v>3.5</v>
+      </c>
+      <c r="C1070">
+        <v>1</v>
+      </c>
+      <c r="D1070">
+        <v>3.5</v>
+      </c>
+      <c r="E1070" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1071" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1071">
+        <v>11</v>
+      </c>
+      <c r="C1071">
+        <v>1</v>
+      </c>
+      <c r="D1071">
+        <v>11</v>
+      </c>
+      <c r="E1071" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1072" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1072">
+        <v>4</v>
+      </c>
+      <c r="C1072">
+        <v>1</v>
+      </c>
+      <c r="D1072">
+        <v>4</v>
+      </c>
+      <c r="E1072" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1073" t="s">
+        <v>345</v>
+      </c>
+      <c r="B1073">
+        <v>14.8</v>
+      </c>
+      <c r="C1073">
+        <v>2</v>
+      </c>
+      <c r="D1073">
+        <v>29.6</v>
+      </c>
+      <c r="E1073" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1074" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1074">
+        <v>8.5</v>
+      </c>
+      <c r="C1074">
+        <v>2</v>
+      </c>
+      <c r="D1074">
+        <v>15</v>
+      </c>
+      <c r="E1074" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1075" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1075">
+        <v>15</v>
+      </c>
+      <c r="C1075">
+        <v>2</v>
+      </c>
+      <c r="D1075">
+        <v>30</v>
+      </c>
+      <c r="E1075" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1076" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1076">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="C1076">
+        <v>1</v>
+      </c>
+      <c r="D1076">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="E1076" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1077" t="s">
+        <v>349</v>
+      </c>
+      <c r="B1077">
+        <v>8</v>
+      </c>
+      <c r="C1077">
+        <v>2</v>
+      </c>
+      <c r="D1077">
+        <v>15</v>
+      </c>
+      <c r="E1077" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1078" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1078">
+        <v>7.51</v>
+      </c>
+      <c r="C1078">
+        <v>2</v>
+      </c>
+      <c r="D1078">
+        <v>15.02</v>
+      </c>
+      <c r="E1078" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1079" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1079">
+        <v>3.9</v>
+      </c>
+      <c r="C1079">
+        <v>1</v>
+      </c>
+      <c r="D1079">
+        <v>3.9</v>
+      </c>
+      <c r="E1079" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1080" t="s">
+        <v>351</v>
+      </c>
+      <c r="B1080">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1080">
+        <v>2</v>
+      </c>
+      <c r="D1080">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E1080" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1081" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1081">
+        <v>2.75</v>
+      </c>
+      <c r="C1081">
+        <v>1</v>
+      </c>
+      <c r="D1081">
+        <v>2.75</v>
+      </c>
+      <c r="E1081" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1082" t="s">
+        <v>352</v>
+      </c>
+      <c r="B1082">
+        <v>5</v>
+      </c>
+      <c r="C1082">
+        <v>2</v>
+      </c>
+      <c r="D1082">
+        <v>10</v>
+      </c>
+      <c r="E1082" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1083" t="s">
+        <v>353</v>
+      </c>
+      <c r="B1083">
+        <v>1</v>
+      </c>
+      <c r="C1083">
+        <v>2</v>
+      </c>
+      <c r="D1083">
+        <v>2</v>
+      </c>
+      <c r="E1083" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1084" t="s">
+        <v>354</v>
+      </c>
+      <c r="B1084">
+        <v>8</v>
+      </c>
+      <c r="C1084">
+        <v>0.8</v>
+      </c>
+      <c r="D1084">
+        <v>6.4</v>
+      </c>
+      <c r="E1084" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1085" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1085">
+        <v>9</v>
+      </c>
+      <c r="C1085">
+        <v>1</v>
+      </c>
+      <c r="D1085">
+        <v>9</v>
+      </c>
+      <c r="E1085" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1086" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1086">
+        <v>6</v>
+      </c>
+      <c r="C1086">
+        <v>2</v>
+      </c>
+      <c r="D1086">
+        <v>12</v>
+      </c>
+      <c r="E1086" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1087" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1087">
+        <v>5.2</v>
+      </c>
+      <c r="C1087">
+        <v>1</v>
+      </c>
+      <c r="D1087">
+        <v>5.2</v>
+      </c>
+      <c r="E1087" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1088" t="s">
+        <v>357</v>
+      </c>
+      <c r="B1088">
+        <v>1</v>
+      </c>
+      <c r="C1088">
+        <v>2</v>
+      </c>
+      <c r="D1088">
+        <v>2</v>
+      </c>
+      <c r="E1088" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1089" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1089">
+        <v>2.75</v>
+      </c>
+      <c r="C1089">
+        <v>3</v>
+      </c>
+      <c r="D1089">
+        <v>8.25</v>
+      </c>
+      <c r="E1089" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1090" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1090">
+        <v>2.75</v>
+      </c>
+      <c r="C1090">
+        <v>3</v>
+      </c>
+      <c r="D1090">
+        <v>8.25</v>
+      </c>
+      <c r="E1090" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1091" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1091">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="C1091">
+        <v>1</v>
+      </c>
+      <c r="D1091">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E1091" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1092" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1092">
+        <v>5.15</v>
+      </c>
+      <c r="C1092">
+        <v>1</v>
+      </c>
+      <c r="D1092">
+        <v>5.15</v>
+      </c>
+      <c r="E1092" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1093" t="s">
+        <v>358</v>
+      </c>
+      <c r="B1093">
+        <v>6</v>
+      </c>
+      <c r="C1093">
+        <v>1</v>
+      </c>
+      <c r="D1093">
+        <v>6</v>
+      </c>
+      <c r="E1093" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1094" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1094">
+        <v>6.9</v>
+      </c>
+      <c r="C1094">
+        <v>0.5</v>
+      </c>
+      <c r="D1094">
+        <v>3.45</v>
+      </c>
+      <c r="E1094" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1095" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1095">
+        <v>0.52</v>
+      </c>
+      <c r="C1095">
+        <v>5</v>
+      </c>
+      <c r="D1095">
+        <v>2.6</v>
+      </c>
+      <c r="E1095" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1096" t="s">
+        <v>359</v>
+      </c>
+      <c r="B1096">
+        <v>4.2</v>
+      </c>
+      <c r="C1096">
+        <v>1</v>
+      </c>
+      <c r="D1096">
+        <v>4.2</v>
+      </c>
+      <c r="E1096" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1097" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1097">
+        <v>1.42</v>
+      </c>
+      <c r="C1097">
+        <v>4</v>
+      </c>
+      <c r="D1097">
+        <v>5.68</v>
+      </c>
+      <c r="E1097" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1098" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1098">
+        <v>1.96</v>
+      </c>
+      <c r="C1098">
+        <v>1</v>
+      </c>
+      <c r="D1098">
+        <v>1.96</v>
+      </c>
+      <c r="E1098" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1099" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1099">
+        <v>2.9</v>
+      </c>
+      <c r="C1099">
+        <v>2</v>
+      </c>
+      <c r="D1099">
+        <v>5.8</v>
+      </c>
+      <c r="E1099" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1100" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1100">
+        <v>1.53</v>
+      </c>
+      <c r="C1100">
+        <v>7</v>
+      </c>
+      <c r="D1100">
+        <v>10.71</v>
+      </c>
+      <c r="E1100" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1101" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1101">
+        <v>5.5</v>
+      </c>
+      <c r="C1101">
+        <v>1</v>
+      </c>
+      <c r="D1101">
+        <v>5.5</v>
+      </c>
+      <c r="E1101" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1102" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1102">
+        <v>3.7</v>
+      </c>
+      <c r="C1102">
+        <v>2</v>
+      </c>
+      <c r="D1102">
+        <v>5</v>
+      </c>
+      <c r="E1102" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1103" t="s">
+        <v>360</v>
+      </c>
+      <c r="B1103">
+        <v>2.73</v>
+      </c>
+      <c r="C1103">
+        <v>2</v>
+      </c>
+      <c r="D1103">
+        <v>5.46</v>
+      </c>
+      <c r="E1103" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1104" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1104">
+        <v>3.5</v>
+      </c>
+      <c r="C1104">
+        <v>1</v>
+      </c>
+      <c r="D1104">
+        <v>3.5</v>
+      </c>
+      <c r="E1104" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1105" t="s">
+        <v>361</v>
+      </c>
+      <c r="B1105">
+        <v>35</v>
+      </c>
+      <c r="C1105">
+        <v>1</v>
+      </c>
+      <c r="D1105">
+        <v>35</v>
+      </c>
+      <c r="E1105" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1106" t="s">
+        <v>362</v>
+      </c>
+      <c r="B1106">
+        <v>16</v>
+      </c>
+      <c r="C1106">
+        <v>1</v>
+      </c>
+      <c r="D1106">
+        <v>16</v>
+      </c>
+      <c r="E1106" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1107" t="s">
+        <v>363</v>
+      </c>
+      <c r="B1107">
+        <v>17.5</v>
+      </c>
+      <c r="C1107">
+        <v>2</v>
+      </c>
+      <c r="D1107">
+        <v>35</v>
+      </c>
+      <c r="E1107" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1108" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1108">
+        <v>5.2</v>
+      </c>
+      <c r="C1108">
+        <v>1</v>
+      </c>
+      <c r="D1108">
+        <v>5.2</v>
+      </c>
+      <c r="E1108" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1109" t="s">
+        <v>364</v>
+      </c>
+      <c r="B1109">
+        <v>1.4</v>
+      </c>
+      <c r="C1109">
+        <v>4</v>
+      </c>
+      <c r="D1109">
+        <v>5.6</v>
+      </c>
+      <c r="E1109" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1110" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1110">
+        <v>5.25</v>
+      </c>
+      <c r="C1110">
+        <v>1</v>
+      </c>
+      <c r="D1110">
+        <v>5.25</v>
+      </c>
+      <c r="E1110" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1111" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1111">
+        <v>2.5</v>
+      </c>
+      <c r="C1111">
+        <v>1</v>
+      </c>
+      <c r="D1111">
+        <v>2.5</v>
+      </c>
+      <c r="E1111" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1112" t="s">
+        <v>366</v>
+      </c>
+      <c r="B1112">
+        <v>4.5</v>
+      </c>
+      <c r="C1112">
+        <v>2</v>
+      </c>
+      <c r="D1112">
+        <v>5.6</v>
+      </c>
+      <c r="E1112" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1113" t="s">
+        <v>215</v>
+      </c>
+      <c r="B1113">
+        <v>5.7</v>
+      </c>
+      <c r="C1113">
+        <v>1</v>
+      </c>
+      <c r="D1113">
+        <v>5.7</v>
+      </c>
+      <c r="E1113" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1114" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1114">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="C1114">
+        <v>1</v>
+      </c>
+      <c r="D1114">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="E1114" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1115" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1115">
+        <v>2.1</v>
+      </c>
+      <c r="C1115">
+        <v>3</v>
+      </c>
+      <c r="D1115">
+        <v>6.3</v>
+      </c>
+      <c r="E1115" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1116" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1116">
+        <v>3.48</v>
+      </c>
+      <c r="C1116">
+        <v>1</v>
+      </c>
+      <c r="D1116">
+        <v>3.48</v>
+      </c>
+      <c r="E1116" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1117" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1117">
+        <v>0.52</v>
+      </c>
+      <c r="C1117">
+        <v>5</v>
+      </c>
+      <c r="D1117">
+        <v>2.6</v>
+      </c>
+      <c r="E1117" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1118" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1118">
+        <v>1.5</v>
+      </c>
+      <c r="C1118">
+        <v>2</v>
+      </c>
+      <c r="D1118">
+        <v>3</v>
+      </c>
+      <c r="E1118" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1119" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1119">
+        <v>3.17</v>
+      </c>
+      <c r="C1119">
+        <v>1</v>
+      </c>
+      <c r="D1119">
+        <v>3.17</v>
+      </c>
+      <c r="E1119" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1120" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1120">
+        <v>1.24</v>
+      </c>
+      <c r="C1120">
+        <v>3</v>
+      </c>
+      <c r="D1120">
+        <v>3.72</v>
+      </c>
+      <c r="E1120" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1121" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1121">
+        <v>12.5</v>
+      </c>
+      <c r="C1121">
+        <v>0.7</v>
+      </c>
+      <c r="D1121">
+        <v>8.75</v>
+      </c>
+      <c r="E1121" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1122" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1122">
+        <v>1.25</v>
+      </c>
+      <c r="C1122">
+        <v>8</v>
+      </c>
+      <c r="D1122">
+        <v>10</v>
+      </c>
+      <c r="E1122" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1123" t="s">
+        <v>334</v>
+      </c>
+      <c r="B1123">
+        <v>2.7</v>
+      </c>
+      <c r="C1123">
+        <v>1</v>
+      </c>
+      <c r="D1123">
+        <v>2.7</v>
+      </c>
+      <c r="E1123" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1124" t="s">
+        <v>360</v>
+      </c>
+      <c r="B1124">
+        <v>2.73</v>
+      </c>
+      <c r="C1124">
+        <v>2</v>
+      </c>
+      <c r="D1124">
+        <v>5.46</v>
+      </c>
+      <c r="E1124" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1125" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1125">
+        <v>3</v>
+      </c>
+      <c r="C1125">
+        <v>1</v>
+      </c>
+      <c r="D1125">
+        <v>3</v>
+      </c>
+      <c r="E1125" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1126" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1126">
+        <v>5.5</v>
+      </c>
+      <c r="C1126">
+        <v>1</v>
+      </c>
+      <c r="D1126">
+        <v>5.5</v>
+      </c>
+      <c r="E1126" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1127" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1127">
+        <v>6</v>
+      </c>
+      <c r="C1127">
+        <v>1</v>
+      </c>
+      <c r="D1127">
+        <v>6</v>
+      </c>
+      <c r="E1127" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1128" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1128">
+        <v>2.5</v>
+      </c>
+      <c r="C1128">
+        <v>2</v>
+      </c>
+      <c r="D1128">
+        <v>5</v>
+      </c>
+      <c r="E1128" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1129" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1129">
+        <v>16</v>
+      </c>
+      <c r="C1129">
+        <v>2</v>
+      </c>
+      <c r="D1129">
+        <v>32</v>
+      </c>
+      <c r="E1129" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1130" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1130">
+        <v>4</v>
+      </c>
+      <c r="C1130">
+        <v>1</v>
+      </c>
+      <c r="D1130">
+        <v>4</v>
+      </c>
+      <c r="E1130" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1131" t="s">
+        <v>354</v>
+      </c>
+      <c r="B1131">
+        <v>11</v>
+      </c>
+      <c r="C1131">
+        <v>1.2</v>
+      </c>
+      <c r="D1131">
+        <v>13.2</v>
+      </c>
+      <c r="E1131" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1132" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1132">
+        <v>9</v>
+      </c>
+      <c r="C1132">
+        <v>0.6</v>
+      </c>
+      <c r="D1132">
+        <v>5.4</v>
+      </c>
+      <c r="E1132" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1133" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1133">
+        <v>11.5</v>
+      </c>
+      <c r="C1133">
+        <v>1</v>
+      </c>
+      <c r="D1133">
+        <v>11.5</v>
+      </c>
+      <c r="E1133" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1134" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1134">
+        <v>5.2</v>
+      </c>
+      <c r="C1134">
+        <v>1</v>
+      </c>
+      <c r="D1134">
+        <v>5.2</v>
+      </c>
+      <c r="E1134" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1135" t="s">
+        <v>315</v>
+      </c>
+      <c r="B1135">
+        <v>1.9</v>
+      </c>
+      <c r="C1135">
+        <v>2</v>
+      </c>
+      <c r="D1135">
+        <v>3.8</v>
+      </c>
+      <c r="E1135" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1136" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1136">
+        <v>6.5</v>
+      </c>
+      <c r="C1136">
+        <v>1</v>
+      </c>
+      <c r="D1136">
+        <v>6.5</v>
+      </c>
+      <c r="E1136" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1137" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1137">
+        <v>3.8</v>
+      </c>
+      <c r="C1137">
+        <v>2</v>
+      </c>
+      <c r="D1137">
+        <v>7.6</v>
+      </c>
+      <c r="E1137" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1138" t="s">
+        <v>372</v>
+      </c>
+      <c r="B1138">
+        <v>3.3</v>
+      </c>
+      <c r="C1138">
+        <v>2</v>
+      </c>
+      <c r="D1138">
+        <v>6.6</v>
+      </c>
+      <c r="E1138" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1139" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1139">
+        <v>3.2</v>
+      </c>
+      <c r="C1139">
+        <v>1</v>
+      </c>
+      <c r="D1139">
+        <v>3.2</v>
+      </c>
+      <c r="E1139" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1140" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1140">
+        <v>5.8</v>
+      </c>
+      <c r="C1140">
+        <v>2</v>
+      </c>
+      <c r="D1140">
+        <v>10</v>
+      </c>
+      <c r="E1140" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1141" t="s">
+        <v>374</v>
+      </c>
+      <c r="B1141">
+        <v>5.8</v>
+      </c>
+      <c r="C1141">
+        <v>1</v>
+      </c>
+      <c r="D1141">
+        <v>5.8</v>
+      </c>
+      <c r="E1141" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1142" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1142">
+        <v>2.98</v>
+      </c>
+      <c r="C1142">
+        <v>1</v>
+      </c>
+      <c r="D1142">
+        <v>2.98</v>
+      </c>
+      <c r="E1142" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1143" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1143">
+        <v>0.7</v>
+      </c>
+      <c r="C1143">
+        <v>5</v>
+      </c>
+      <c r="D1143">
+        <v>3.5</v>
+      </c>
+      <c r="E1143" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1144" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1144">
+        <v>1.06</v>
+      </c>
+      <c r="C1144">
+        <v>3</v>
+      </c>
+      <c r="D1144">
+        <v>3.18</v>
+      </c>
+      <c r="E1144" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1145" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1145">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C1145">
+        <v>1</v>
+      </c>
+      <c r="D1145">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E1145" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1146" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1146">
+        <v>1.53</v>
+      </c>
+      <c r="C1146">
+        <v>5</v>
+      </c>
+      <c r="D1146">
+        <v>7.65</v>
+      </c>
+      <c r="E1146" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1147" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1147">
+        <v>3.7</v>
+      </c>
+      <c r="C1147">
+        <v>2</v>
+      </c>
+      <c r="D1147">
+        <v>5</v>
+      </c>
+      <c r="E1147" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1148" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1148">
+        <v>18.75</v>
+      </c>
+      <c r="C1148">
+        <v>1</v>
+      </c>
+      <c r="D1148">
+        <v>18.75</v>
+      </c>
+      <c r="E1148" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1149" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1149">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="C1149">
+        <v>1</v>
+      </c>
+      <c r="D1149">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="E1149" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1150" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1150">
+        <v>30</v>
+      </c>
+      <c r="C1150">
+        <v>1.2</v>
+      </c>
+      <c r="D1150">
+        <v>36</v>
+      </c>
+      <c r="E1150" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1151" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1151">
+        <v>12</v>
+      </c>
+      <c r="C1151">
+        <v>0.3</v>
+      </c>
+      <c r="D1151">
+        <v>3.6</v>
+      </c>
+      <c r="E1151" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1152" t="s">
+        <v>376</v>
+      </c>
+      <c r="B1152">
+        <v>11</v>
+      </c>
+      <c r="C1152">
+        <v>2</v>
+      </c>
+      <c r="D1152">
+        <v>22</v>
+      </c>
+      <c r="E1152" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1153" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1153">
+        <v>7.7</v>
+      </c>
+      <c r="C1153">
+        <v>2</v>
+      </c>
+      <c r="D1153">
+        <v>15.4</v>
+      </c>
+      <c r="E1153" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1154" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1154">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1154">
+        <v>2</v>
+      </c>
+      <c r="D1154">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E1154" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1155" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1155">
+        <v>5.5</v>
+      </c>
+      <c r="C1155">
+        <v>2</v>
+      </c>
+      <c r="D1155">
+        <v>11</v>
+      </c>
+      <c r="E1155" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1156" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1156">
+        <v>5.5</v>
+      </c>
+      <c r="C1156">
+        <v>2</v>
+      </c>
+      <c r="D1156">
+        <v>11</v>
+      </c>
+      <c r="E1156" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1157" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1157">
+        <v>5</v>
+      </c>
+      <c r="C1157">
+        <v>1</v>
+      </c>
+      <c r="D1157">
+        <v>5</v>
+      </c>
+      <c r="E1157" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1158" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1158">
+        <v>7.6</v>
+      </c>
+      <c r="C1158">
+        <v>1</v>
+      </c>
+      <c r="D1158">
+        <v>7.6</v>
+      </c>
+      <c r="E1158" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1159" t="s">
+        <v>316</v>
+      </c>
+      <c r="B1159">
+        <v>7.6</v>
+      </c>
+      <c r="C1159">
+        <v>1</v>
+      </c>
+      <c r="D1159">
+        <v>7.6</v>
+      </c>
+      <c r="E1159" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1160" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1160">
+        <v>5</v>
+      </c>
+      <c r="C1160">
+        <v>1</v>
+      </c>
+      <c r="D1160">
+        <v>5</v>
+      </c>
+      <c r="E1160" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1161" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1161">
+        <v>4.8</v>
+      </c>
+      <c r="C1161">
+        <v>2</v>
+      </c>
+      <c r="D1161">
+        <v>9.6</v>
+      </c>
+      <c r="E1161" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1162" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1162">
+        <v>1.9</v>
+      </c>
+      <c r="C1162">
+        <v>2</v>
+      </c>
+      <c r="D1162">
+        <v>3.8</v>
+      </c>
+      <c r="E1162" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1163" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1163">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1163">
+        <v>2</v>
+      </c>
+      <c r="D1163">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E1163" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1164" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1164">
+        <v>1</v>
+      </c>
+      <c r="C1164">
+        <v>2</v>
+      </c>
+      <c r="D1164">
+        <v>2</v>
+      </c>
+      <c r="E1164" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1165" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1165">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1165">
+        <v>1</v>
+      </c>
+      <c r="D1165">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E1165" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1166" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1166">
+        <v>6.5</v>
+      </c>
+      <c r="C1166">
+        <v>1</v>
+      </c>
+      <c r="D1166">
+        <v>6.5</v>
+      </c>
+      <c r="E1166" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1167" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1167">
+        <v>8</v>
+      </c>
+      <c r="C1167">
+        <v>1</v>
+      </c>
+      <c r="D1167">
+        <v>8</v>
+      </c>
+      <c r="E1167" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1168" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1168">
+        <v>3</v>
+      </c>
+      <c r="C1168">
+        <v>2</v>
+      </c>
+      <c r="D1168">
+        <v>6</v>
+      </c>
+      <c r="E1168" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1169" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1169">
+        <v>2.4</v>
+      </c>
+      <c r="C1169">
+        <v>2</v>
+      </c>
+      <c r="D1169">
+        <v>4.8</v>
+      </c>
+      <c r="E1169" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1170" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1170">
+        <v>3.3</v>
+      </c>
+      <c r="C1170">
+        <v>1</v>
+      </c>
+      <c r="D1170">
+        <v>3.3</v>
+      </c>
+      <c r="E1170" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1171" t="s">
+        <v>325</v>
+      </c>
+      <c r="B1171">
+        <v>14</v>
+      </c>
+      <c r="C1171">
+        <v>1</v>
+      </c>
+      <c r="D1171">
+        <v>14</v>
+      </c>
+      <c r="E1171" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1172" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1172">
+        <v>4</v>
+      </c>
+      <c r="C1172">
+        <v>1</v>
+      </c>
+      <c r="D1172">
+        <v>4</v>
+      </c>
+      <c r="E1172" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1173" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1173">
+        <v>3.8</v>
+      </c>
+      <c r="C1173">
+        <v>2</v>
+      </c>
+      <c r="D1173">
+        <v>7.6</v>
+      </c>
+      <c r="E1173" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1174" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1174">
+        <v>3.2</v>
+      </c>
+      <c r="C1174">
+        <v>1</v>
+      </c>
+      <c r="D1174">
+        <v>3.2</v>
+      </c>
+      <c r="E1174" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1175" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1175">
+        <v>1.5</v>
+      </c>
+      <c r="C1175">
+        <v>4</v>
+      </c>
+      <c r="D1175">
+        <v>6</v>
+      </c>
+      <c r="E1175" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1176" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1176">
+        <v>1.5</v>
+      </c>
+      <c r="C1176">
+        <v>4</v>
+      </c>
+      <c r="D1176">
+        <v>6</v>
+      </c>
+      <c r="E1176" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1177" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1177">
+        <v>6.9</v>
+      </c>
+      <c r="C1177">
+        <v>0.25</v>
+      </c>
+      <c r="D1177">
+        <v>1.73</v>
+      </c>
+      <c r="E1177" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1178" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1178">
+        <v>2.48</v>
+      </c>
+      <c r="C1178">
+        <v>1</v>
+      </c>
+      <c r="D1178">
+        <v>2.48</v>
+      </c>
+      <c r="E1178" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1179" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1179">
+        <v>0.88</v>
+      </c>
+      <c r="C1179">
+        <v>4</v>
+      </c>
+      <c r="D1179">
+        <v>3.52</v>
+      </c>
+      <c r="E1179" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1180" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1180">
+        <v>2.75</v>
+      </c>
+      <c r="C1180">
+        <v>1</v>
+      </c>
+      <c r="D1180">
+        <v>2.75</v>
+      </c>
+      <c r="E1180" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1181" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1181">
+        <v>1.42</v>
+      </c>
+      <c r="C1181">
+        <v>4</v>
+      </c>
+      <c r="D1181">
+        <v>5.68</v>
+      </c>
+      <c r="E1181" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1182" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1182">
+        <v>1.56</v>
+      </c>
+      <c r="C1182">
+        <v>1</v>
+      </c>
+      <c r="D1182">
+        <v>1.56</v>
+      </c>
+      <c r="E1182" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1183" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1183">
+        <v>6.3</v>
+      </c>
+      <c r="C1183">
+        <v>1</v>
+      </c>
+      <c r="D1183">
+        <v>6.3</v>
+      </c>
+      <c r="E1183" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1184" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1184">
+        <v>3.8</v>
+      </c>
+      <c r="C1184">
+        <v>1</v>
+      </c>
+      <c r="D1184">
+        <v>3.8</v>
+      </c>
+      <c r="E1184" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1185" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1185">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C1185">
+        <v>1</v>
+      </c>
+      <c r="D1185">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E1185" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1186" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1186">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C1186">
+        <v>5</v>
+      </c>
+      <c r="D1186">
+        <v>5.55</v>
+      </c>
+      <c r="E1186" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1187" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1187">
+        <v>2.5</v>
+      </c>
+      <c r="C1187">
+        <v>1</v>
+      </c>
+      <c r="D1187">
+        <v>2.5</v>
+      </c>
+      <c r="E1187" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1188" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1188">
+        <v>3</v>
+      </c>
+      <c r="C1188">
+        <v>1</v>
+      </c>
+      <c r="D1188">
+        <v>3</v>
+      </c>
+      <c r="E1188" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1189" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1189">
+        <v>5.5</v>
+      </c>
+      <c r="C1189">
+        <v>1</v>
+      </c>
+      <c r="D1189">
+        <v>5.5</v>
+      </c>
+      <c r="E1189" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1190" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1190">
+        <v>3.5</v>
+      </c>
+      <c r="C1190">
+        <v>1</v>
+      </c>
+      <c r="D1190">
+        <v>3.5</v>
+      </c>
+      <c r="E1190" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1191" t="s">
+        <v>339</v>
+      </c>
+      <c r="B1191">
+        <v>3.2</v>
+      </c>
+      <c r="C1191">
+        <v>1</v>
+      </c>
+      <c r="D1191">
+        <v>3.2</v>
+      </c>
+      <c r="E1191" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1192" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1192">
+        <v>3.2</v>
+      </c>
+      <c r="C1192">
+        <v>1</v>
+      </c>
+      <c r="D1192">
+        <v>3.2</v>
+      </c>
+      <c r="E1192" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1193" t="s">
+        <v>340</v>
+      </c>
+      <c r="B1193">
+        <v>3.5</v>
+      </c>
+      <c r="C1193">
+        <v>1</v>
+      </c>
+      <c r="D1193">
+        <v>3.5</v>
+      </c>
+      <c r="E1193" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1194" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1194">
+        <v>2.5</v>
+      </c>
+      <c r="C1194">
+        <v>1</v>
+      </c>
+      <c r="D1194">
+        <v>2.5</v>
+      </c>
+      <c r="E1194" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1195" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1195">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="C1195">
+        <v>1</v>
+      </c>
+      <c r="D1195">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E1195" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1196" t="s">
+        <v>383</v>
+      </c>
+      <c r="B1196">
+        <v>5.5</v>
+      </c>
+      <c r="C1196">
+        <v>1</v>
+      </c>
+      <c r="D1196">
+        <v>5.5</v>
+      </c>
+      <c r="E1196" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1197" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1197">
+        <v>12.5</v>
+      </c>
+      <c r="C1197">
+        <v>1</v>
+      </c>
+      <c r="D1197">
+        <v>12.5</v>
+      </c>
+      <c r="E1197" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1198" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1198">
+        <v>2.5</v>
+      </c>
+      <c r="C1198">
+        <v>1</v>
+      </c>
+      <c r="D1198">
+        <v>2.5</v>
+      </c>
+      <c r="E1198" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1199" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1199">
+        <v>5</v>
+      </c>
+      <c r="C1199">
+        <v>1</v>
+      </c>
+      <c r="D1199">
+        <v>5</v>
+      </c>
+      <c r="E1199" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1200" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1200">
+        <v>7.7</v>
+      </c>
+      <c r="C1200">
+        <v>1</v>
+      </c>
+      <c r="D1200">
+        <v>7.7</v>
+      </c>
+      <c r="E1200" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1201" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1201">
+        <v>2</v>
+      </c>
+      <c r="C1201">
+        <v>4</v>
+      </c>
+      <c r="D1201">
+        <v>8</v>
+      </c>
+      <c r="E1201" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1202" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1202">
+        <v>3.5</v>
+      </c>
+      <c r="C1202">
+        <v>2</v>
+      </c>
+      <c r="D1202">
+        <v>7</v>
+      </c>
+      <c r="E1202" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1203" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1203">
+        <v>2.7</v>
+      </c>
+      <c r="C1203">
+        <v>1</v>
+      </c>
+      <c r="D1203">
+        <v>2.7</v>
+      </c>
+      <c r="E1203" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1204" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1204">
+        <v>3.05</v>
+      </c>
+      <c r="C1204">
+        <v>1</v>
+      </c>
+      <c r="D1204">
+        <v>3.05</v>
+      </c>
+      <c r="E1204" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1205" t="s">
+        <v>345</v>
+      </c>
+      <c r="B1205">
+        <v>14.8</v>
+      </c>
+      <c r="C1205">
+        <v>1</v>
+      </c>
+      <c r="D1205">
+        <v>14.8</v>
+      </c>
+      <c r="E1205" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1206" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1206">
+        <v>18</v>
+      </c>
+      <c r="C1206">
+        <v>2</v>
+      </c>
+      <c r="D1206">
+        <v>36</v>
+      </c>
+      <c r="E1206" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1207" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1207">
+        <v>19</v>
+      </c>
+      <c r="C1207">
+        <v>1</v>
+      </c>
+      <c r="D1207">
+        <v>19</v>
+      </c>
+      <c r="E1207" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1208" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1208">
+        <v>7.51</v>
+      </c>
+      <c r="C1208">
+        <v>2</v>
+      </c>
+      <c r="D1208">
+        <v>15.02</v>
+      </c>
+      <c r="E1208" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1209" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1209">
+        <v>3.9</v>
+      </c>
+      <c r="C1209">
+        <v>1</v>
+      </c>
+      <c r="D1209">
+        <v>3.9</v>
+      </c>
+      <c r="E1209" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1210" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1210">
+        <v>2.5</v>
+      </c>
+      <c r="C1210">
+        <v>1</v>
+      </c>
+      <c r="D1210">
+        <v>2.5</v>
+      </c>
+      <c r="E1210" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1211" t="s">
+        <v>351</v>
+      </c>
+      <c r="B1211">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1211">
+        <v>3</v>
+      </c>
+      <c r="D1211">
+        <v>6.6</v>
+      </c>
+      <c r="E1211" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1212" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1212">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C1212">
+        <v>2</v>
+      </c>
+      <c r="D1212">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E1212" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1213" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1213">
+        <v>4</v>
+      </c>
+      <c r="C1213">
+        <v>1</v>
+      </c>
+      <c r="D1213">
+        <v>4</v>
+      </c>
+      <c r="E1213" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1214" t="s">
+        <v>387</v>
+      </c>
+      <c r="B1214">
+        <v>10</v>
+      </c>
+      <c r="C1214">
+        <v>1</v>
+      </c>
+      <c r="D1214">
+        <v>10</v>
+      </c>
+      <c r="E1214" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1215" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1215">
+        <v>34</v>
+      </c>
+      <c r="C1215">
+        <v>1</v>
+      </c>
+      <c r="D1215">
+        <v>34</v>
+      </c>
+      <c r="E1215" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1216" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1216">
+        <v>30</v>
+      </c>
+      <c r="C1216">
+        <v>0.2</v>
+      </c>
+      <c r="D1216">
+        <v>6</v>
+      </c>
+      <c r="E1216" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1217" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1217">
+        <v>11.5</v>
+      </c>
+      <c r="C1217">
+        <v>2</v>
+      </c>
+      <c r="D1217">
+        <v>23</v>
+      </c>
+      <c r="E1217" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1218" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1218">
+        <v>5.5</v>
+      </c>
+      <c r="C1218">
+        <v>2</v>
+      </c>
+      <c r="D1218">
+        <v>11</v>
+      </c>
+      <c r="E1218" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1219" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1219">
+        <v>6</v>
+      </c>
+      <c r="C1219">
+        <v>2</v>
+      </c>
+      <c r="D1219">
+        <v>12</v>
+      </c>
+      <c r="E1219" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1220" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1220">
+        <v>4</v>
+      </c>
+      <c r="C1220">
+        <v>1</v>
+      </c>
+      <c r="D1220">
+        <v>4</v>
+      </c>
+      <c r="E1220" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1221" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1221">
+        <v>11.5</v>
+      </c>
+      <c r="C1221">
+        <v>1</v>
+      </c>
+      <c r="D1221">
+        <v>11.5</v>
+      </c>
+      <c r="E1221" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1222" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1222">
+        <v>6.2</v>
+      </c>
+      <c r="C1222">
+        <v>4</v>
+      </c>
+      <c r="D1222">
+        <v>24.8</v>
+      </c>
+      <c r="E1222" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1223" t="s">
+        <v>391</v>
+      </c>
+      <c r="B1223">
+        <v>3</v>
+      </c>
+      <c r="C1223">
+        <v>1</v>
+      </c>
+      <c r="D1223">
+        <v>3</v>
+      </c>
+      <c r="E1223" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1224" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1224">
+        <v>8.5</v>
+      </c>
+      <c r="C1224">
+        <v>2</v>
+      </c>
+      <c r="D1224">
+        <v>17</v>
+      </c>
+      <c r="E1224" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1225" t="s">
+        <v>316</v>
+      </c>
+      <c r="B1225">
+        <v>7.6</v>
+      </c>
+      <c r="C1225">
+        <v>2</v>
+      </c>
+      <c r="D1225">
+        <v>15.2</v>
+      </c>
+      <c r="E1225" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1226" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1226">
+        <v>4</v>
+      </c>
+      <c r="C1226">
+        <v>1</v>
+      </c>
+      <c r="D1226">
+        <v>4</v>
+      </c>
+      <c r="E1226" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1227" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1227">
+        <v>1.4</v>
+      </c>
+      <c r="C1227">
+        <v>2</v>
+      </c>
+      <c r="D1227">
+        <v>2.8</v>
+      </c>
+      <c r="E1227" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1228" t="s">
+        <v>364</v>
+      </c>
+      <c r="B1228">
+        <v>1.4</v>
+      </c>
+      <c r="C1228">
+        <v>2</v>
+      </c>
+      <c r="D1228">
+        <v>2.8</v>
+      </c>
+      <c r="E1228" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1229" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1229">
+        <v>1.4</v>
+      </c>
+      <c r="C1229">
+        <v>2</v>
+      </c>
+      <c r="D1229">
+        <v>2.8</v>
+      </c>
+      <c r="E1229" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1230" t="s">
+        <v>393</v>
+      </c>
+      <c r="B1230">
+        <v>1.4</v>
+      </c>
+      <c r="C1230">
+        <v>2</v>
+      </c>
+      <c r="D1230">
+        <v>2.8</v>
+      </c>
+      <c r="E1230" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1231" t="s">
+        <v>394</v>
+      </c>
+      <c r="B1231">
+        <v>1.4</v>
+      </c>
+      <c r="C1231">
+        <v>1</v>
+      </c>
+      <c r="D1231">
+        <v>1.4</v>
+      </c>
+      <c r="E1231" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1232" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1232">
+        <v>1.6</v>
+      </c>
+      <c r="C1232">
+        <v>1</v>
+      </c>
+      <c r="D1232">
+        <v>1.6</v>
+      </c>
+      <c r="E1232" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1233" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1233">
+        <v>1.9</v>
+      </c>
+      <c r="C1233">
+        <v>2</v>
+      </c>
+      <c r="D1233">
+        <v>3.8</v>
+      </c>
+      <c r="E1233" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1234" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1234">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1234">
+        <v>2</v>
+      </c>
+      <c r="D1234">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E1234" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1235" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1235">
+        <v>1</v>
+      </c>
+      <c r="C1235">
+        <v>2</v>
+      </c>
+      <c r="D1235">
+        <v>2</v>
+      </c>
+      <c r="E1235" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1236" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1236">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1236">
+        <v>2</v>
+      </c>
+      <c r="D1236">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E1236" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1237" t="s">
+        <v>320</v>
+      </c>
+      <c r="B1237">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1237">
+        <v>2</v>
+      </c>
+      <c r="D1237">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E1237" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1238" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1238">
+        <v>6.5</v>
+      </c>
+      <c r="C1238">
+        <v>1</v>
+      </c>
+      <c r="D1238">
+        <v>6.5</v>
+      </c>
+      <c r="E1238" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1239" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1239">
+        <v>5</v>
+      </c>
+      <c r="C1239">
+        <v>2</v>
+      </c>
+      <c r="D1239">
+        <v>7</v>
+      </c>
+      <c r="E1239" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1240" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1240">
+        <v>1.85</v>
+      </c>
+      <c r="C1240">
+        <v>1</v>
+      </c>
+      <c r="D1240">
+        <v>1.85</v>
+      </c>
+      <c r="E1240" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1241" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1241">
+        <v>8</v>
+      </c>
+      <c r="C1241">
+        <v>2</v>
+      </c>
+      <c r="D1241">
+        <v>15</v>
+      </c>
+      <c r="E1241" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1242" t="s">
+        <v>395</v>
+      </c>
+      <c r="B1242">
+        <v>7.75</v>
+      </c>
+      <c r="C1242">
+        <v>1</v>
+      </c>
+      <c r="D1242">
+        <v>7.75</v>
+      </c>
+      <c r="E1242" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1243" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1243">
+        <v>8</v>
+      </c>
+      <c r="C1243">
+        <v>1</v>
+      </c>
+      <c r="D1243">
+        <v>8</v>
+      </c>
+      <c r="E1243" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1244" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1244">
+        <v>13</v>
+      </c>
+      <c r="C1244">
+        <v>1</v>
+      </c>
+      <c r="D1244">
+        <v>13</v>
+      </c>
+      <c r="E1244" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1245" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1245">
+        <v>6.95</v>
+      </c>
+      <c r="C1245">
+        <v>1</v>
+      </c>
+      <c r="D1245">
+        <v>6.95</v>
+      </c>
+      <c r="E1245" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1246" t="s">
+        <v>397</v>
+      </c>
+      <c r="B1246">
+        <v>1.95</v>
+      </c>
+      <c r="C1246">
+        <v>1</v>
+      </c>
+      <c r="D1246">
+        <v>1.95</v>
+      </c>
+      <c r="E1246" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1247" t="s">
+        <v>398</v>
+      </c>
+      <c r="B1247">
+        <v>4.8</v>
+      </c>
+      <c r="C1247">
+        <v>1</v>
+      </c>
+      <c r="D1247">
+        <v>4.8</v>
+      </c>
+      <c r="E1247" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1248" t="s">
+        <v>399</v>
+      </c>
+      <c r="B1248">
+        <v>5.2</v>
+      </c>
+      <c r="C1248">
+        <v>1</v>
+      </c>
+      <c r="D1248">
+        <v>5.2</v>
+      </c>
+      <c r="E1248" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1249" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1249">
+        <v>3.8</v>
+      </c>
+      <c r="C1249">
+        <v>1</v>
+      </c>
+      <c r="D1249">
+        <v>3.8</v>
+      </c>
+      <c r="E1249" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1250" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1250">
+        <v>3.2</v>
+      </c>
+      <c r="C1250">
+        <v>1</v>
+      </c>
+      <c r="D1250">
+        <v>3.2</v>
+      </c>
+      <c r="E1250" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1251" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1251">
+        <v>1.8</v>
+      </c>
+      <c r="C1251">
+        <v>6</v>
+      </c>
+      <c r="D1251">
+        <v>10.8</v>
+      </c>
+      <c r="E1251" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1252" t="s">
+        <v>401</v>
+      </c>
+      <c r="B1252">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="C1252">
+        <v>1</v>
+      </c>
+      <c r="D1252">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E1252" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1253" t="s">
+        <v>402</v>
+      </c>
+      <c r="B1253">
+        <v>3.7</v>
+      </c>
+      <c r="C1253">
+        <v>2</v>
+      </c>
+      <c r="D1253">
+        <v>7.4</v>
+      </c>
+      <c r="E1253" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1254" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1254">
+        <v>6.9</v>
+      </c>
+      <c r="C1254">
+        <v>0.25</v>
+      </c>
+      <c r="D1254">
+        <v>1.73</v>
+      </c>
+      <c r="E1254" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1255" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1255">
+        <v>2.48</v>
+      </c>
+      <c r="C1255">
+        <v>2</v>
+      </c>
+      <c r="D1255">
+        <v>4.96</v>
+      </c>
+      <c r="E1255" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1256" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1256">
+        <v>0.7</v>
+      </c>
+      <c r="C1256">
+        <v>5</v>
+      </c>
+      <c r="D1256">
+        <v>3.5</v>
+      </c>
+      <c r="E1256" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1257" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1257">
+        <v>1</v>
+      </c>
+      <c r="C1257">
+        <v>2</v>
+      </c>
+      <c r="D1257">
+        <v>2</v>
+      </c>
+      <c r="E1257" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1258" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1258">
+        <v>4.5</v>
+      </c>
+      <c r="C1258">
+        <v>1</v>
+      </c>
+      <c r="D1258">
+        <v>4.5</v>
+      </c>
+      <c r="E1258" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1259" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1259">
+        <v>1.5</v>
+      </c>
+      <c r="C1259">
+        <v>2</v>
+      </c>
+      <c r="D1259">
+        <v>3</v>
+      </c>
+      <c r="E1259" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1260" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1260">
+        <v>1.82</v>
+      </c>
+      <c r="C1260">
+        <v>1</v>
+      </c>
+      <c r="D1260">
+        <v>1.82</v>
+      </c>
+      <c r="E1260" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1261" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1261">
+        <v>2.75</v>
+      </c>
+      <c r="C1261">
+        <v>1</v>
+      </c>
+      <c r="D1261">
+        <v>2.75</v>
+      </c>
+      <c r="E1261" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1262" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1262">
+        <v>1.02</v>
+      </c>
+      <c r="C1262">
+        <v>2</v>
+      </c>
+      <c r="D1262">
+        <v>2.04</v>
+      </c>
+      <c r="E1262" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1263" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1263">
+        <v>1.42</v>
+      </c>
+      <c r="C1263">
+        <v>3</v>
+      </c>
+      <c r="D1263">
+        <v>4.26</v>
+      </c>
+      <c r="E1263" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1264" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1264">
+        <v>1.75</v>
+      </c>
+      <c r="C1264">
+        <v>1</v>
+      </c>
+      <c r="D1264">
+        <v>1.75</v>
+      </c>
+      <c r="E1264" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1265" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1265">
+        <v>0.47</v>
+      </c>
+      <c r="C1265">
+        <v>2</v>
+      </c>
+      <c r="D1265">
+        <v>0.94</v>
+      </c>
+      <c r="E1265" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1266" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1266">
+        <v>2.9</v>
+      </c>
+      <c r="C1266">
+        <v>1</v>
+      </c>
+      <c r="D1266">
+        <v>2.9</v>
+      </c>
+      <c r="E1266" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1267" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1267">
+        <v>1.2</v>
+      </c>
+      <c r="C1267">
+        <v>1</v>
+      </c>
+      <c r="D1267">
+        <v>1.2</v>
+      </c>
+      <c r="E1267" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1268" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1268">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1268">
+        <v>1</v>
+      </c>
+      <c r="D1268">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E1268" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1269" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1269">
+        <v>1.81</v>
+      </c>
+      <c r="C1269">
+        <v>5</v>
+      </c>
+      <c r="D1269">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="E1269" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1270" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1270">
+        <v>4.5</v>
+      </c>
+      <c r="C1270">
+        <v>1</v>
+      </c>
+      <c r="D1270">
+        <v>4.5</v>
+      </c>
+      <c r="E1270" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1271" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1271">
+        <v>2</v>
+      </c>
+      <c r="C1271">
+        <v>1</v>
+      </c>
+      <c r="D1271">
+        <v>2</v>
+      </c>
+      <c r="E1271" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1272" t="s">
+        <v>360</v>
+      </c>
+      <c r="B1272">
+        <v>2.23</v>
+      </c>
+      <c r="C1272">
+        <v>1</v>
+      </c>
+      <c r="D1272">
+        <v>2.23</v>
+      </c>
+      <c r="E1272" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1273" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1273">
+        <v>3</v>
+      </c>
+      <c r="C1273">
+        <v>1</v>
+      </c>
+      <c r="D1273">
+        <v>3</v>
+      </c>
+      <c r="E1273" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1274" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1274">
+        <v>2.5</v>
+      </c>
+      <c r="C1274">
+        <v>1</v>
+      </c>
+      <c r="D1274">
+        <v>2.5</v>
+      </c>
+      <c r="E1274" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1275" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1275">
+        <v>3.2</v>
+      </c>
+      <c r="C1275">
+        <v>1</v>
+      </c>
+      <c r="D1275">
+        <v>3.2</v>
+      </c>
+      <c r="E1275" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1276" t="s">
+        <v>340</v>
+      </c>
+      <c r="B1276">
+        <v>3</v>
+      </c>
+      <c r="C1276">
+        <v>1</v>
+      </c>
+      <c r="D1276">
+        <v>3</v>
+      </c>
+      <c r="E1276" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1277" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1277">
+        <v>2</v>
+      </c>
+      <c r="C1277">
+        <v>2</v>
+      </c>
+      <c r="D1277">
+        <v>4</v>
+      </c>
+      <c r="E1277" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1278" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1278">
+        <v>4</v>
+      </c>
+      <c r="C1278">
+        <v>1</v>
+      </c>
+      <c r="D1278">
+        <v>4</v>
+      </c>
+      <c r="E1278" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1279" t="s">
+        <v>403</v>
+      </c>
+      <c r="B1279">
+        <v>6</v>
+      </c>
+      <c r="C1279">
+        <v>2</v>
+      </c>
+      <c r="D1279">
+        <v>12</v>
+      </c>
+      <c r="E1279" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1280" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1280">
+        <v>7.7</v>
+      </c>
+      <c r="C1280">
+        <v>1</v>
+      </c>
+      <c r="D1280">
+        <v>7.7</v>
+      </c>
+      <c r="E1280" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1281" t="s">
+        <v>224</v>
+      </c>
+      <c r="B1281">
+        <v>13.3</v>
+      </c>
+      <c r="C1281">
+        <v>1</v>
+      </c>
+      <c r="D1281">
+        <v>13.3</v>
+      </c>
+      <c r="E1281" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1282" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1282">
+        <v>2</v>
+      </c>
+      <c r="C1282">
+        <v>3</v>
+      </c>
+      <c r="D1282">
+        <v>6</v>
+      </c>
+      <c r="E1282" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1283" t="s">
+        <v>404</v>
+      </c>
+      <c r="B1283">
+        <v>1.75</v>
+      </c>
+      <c r="C1283">
+        <v>2</v>
+      </c>
+      <c r="D1283">
+        <v>3.5</v>
+      </c>
+      <c r="E1283" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1284" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1284">
+        <v>2.5</v>
+      </c>
+      <c r="C1284">
+        <v>2</v>
+      </c>
+      <c r="D1284">
+        <v>5</v>
+      </c>
+      <c r="E1284" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1285" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1285">
+        <v>18</v>
+      </c>
+      <c r="C1285">
+        <v>2</v>
+      </c>
+      <c r="D1285">
+        <v>36</v>
+      </c>
+      <c r="E1285" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1286" t="s">
+        <v>362</v>
+      </c>
+      <c r="B1286">
+        <v>14</v>
+      </c>
+      <c r="C1286">
+        <v>1</v>
+      </c>
+      <c r="D1286">
+        <v>14</v>
+      </c>
+      <c r="E1286" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1287" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1287">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="C1287">
+        <v>1</v>
+      </c>
+      <c r="D1287">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="E1287" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1288" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1288">
+        <v>3.9</v>
+      </c>
+      <c r="C1288">
+        <v>2</v>
+      </c>
+      <c r="D1288">
+        <v>7.8</v>
+      </c>
+      <c r="E1288" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1289" t="s">
+        <v>351</v>
+      </c>
+      <c r="B1289">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1289">
+        <v>3</v>
+      </c>
+      <c r="D1289">
+        <v>6.6</v>
+      </c>
+      <c r="E1289" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1290" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1290">
+        <v>30</v>
+      </c>
+      <c r="C1290">
+        <v>1</v>
+      </c>
+      <c r="D1290">
+        <v>30</v>
+      </c>
+      <c r="E1290" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1291" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1291">
+        <v>5.6</v>
+      </c>
+      <c r="C1291">
+        <v>1</v>
+      </c>
+      <c r="D1291">
+        <v>5.6</v>
+      </c>
+      <c r="E1291" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1292" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1292">
+        <v>6</v>
+      </c>
+      <c r="C1292">
+        <v>2</v>
+      </c>
+      <c r="D1292">
+        <v>12</v>
+      </c>
+      <c r="E1292" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1293" t="s">
+        <v>406</v>
+      </c>
+      <c r="B1293">
+        <v>4</v>
+      </c>
+      <c r="C1293">
+        <v>1</v>
+      </c>
+      <c r="D1293">
+        <v>4</v>
+      </c>
+      <c r="E1293" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1294" t="s">
+        <v>395</v>
+      </c>
+      <c r="B1294">
+        <v>7.75</v>
+      </c>
+      <c r="C1294">
+        <v>2</v>
+      </c>
+      <c r="D1294">
+        <v>15.5</v>
+      </c>
+      <c r="E1294" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1295" t="s">
+        <v>407</v>
+      </c>
+      <c r="B1295">
+        <v>2</v>
+      </c>
+      <c r="C1295">
+        <v>1</v>
+      </c>
+      <c r="D1295">
+        <v>2</v>
+      </c>
+      <c r="E1295" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1296" t="s">
+        <v>408</v>
+      </c>
+      <c r="B1296">
+        <v>2</v>
+      </c>
+      <c r="C1296">
+        <v>1</v>
+      </c>
+      <c r="D1296">
+        <v>1.75</v>
+      </c>
+      <c r="E1296" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1297" t="s">
+        <v>409</v>
+      </c>
+      <c r="B1297">
+        <v>2</v>
+      </c>
+      <c r="C1297">
+        <v>1</v>
+      </c>
+      <c r="D1297">
+        <v>1.75</v>
+      </c>
+      <c r="E1297" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1298" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1298">
+        <v>3.8</v>
+      </c>
+      <c r="C1298">
+        <v>2</v>
+      </c>
+      <c r="D1298">
+        <v>7.6</v>
+      </c>
+      <c r="E1298" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1299" t="s">
+        <v>328</v>
+      </c>
+      <c r="B1299">
+        <v>3.4</v>
+      </c>
+      <c r="C1299">
+        <v>2</v>
+      </c>
+      <c r="D1299">
+        <v>6.8</v>
+      </c>
+      <c r="E1299" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1300" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1300">
+        <v>3.2</v>
+      </c>
+      <c r="C1300">
+        <v>1</v>
+      </c>
+      <c r="D1300">
+        <v>3.2</v>
+      </c>
+      <c r="E1300" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1301" t="s">
+        <v>410</v>
+      </c>
+      <c r="B1301">
+        <v>3</v>
+      </c>
+      <c r="C1301">
+        <v>2</v>
+      </c>
+      <c r="D1301">
+        <v>6</v>
+      </c>
+      <c r="E1301" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1302" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1302">
+        <v>0.88</v>
+      </c>
+      <c r="C1302">
+        <v>5</v>
+      </c>
+      <c r="D1302">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E1302" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1303" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1303">
+        <v>4.5</v>
+      </c>
+      <c r="C1303">
+        <v>1</v>
+      </c>
+      <c r="D1303">
+        <v>4.5</v>
+      </c>
+      <c r="E1303" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1304" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1304">
+        <v>1.5</v>
+      </c>
+      <c r="C1304">
+        <v>2</v>
+      </c>
+      <c r="D1304">
+        <v>3</v>
+      </c>
+      <c r="E1304" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1305" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1305">
+        <v>1.42</v>
+      </c>
+      <c r="C1305">
+        <v>1</v>
+      </c>
+      <c r="D1305">
+        <v>1.42</v>
+      </c>
+      <c r="E1305" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1306" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1306">
+        <v>12.9</v>
+      </c>
+      <c r="C1306">
+        <v>0.4</v>
+      </c>
+      <c r="D1306">
+        <v>5.16</v>
+      </c>
+      <c r="E1306" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1307" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1307">
+        <v>0.31</v>
+      </c>
+      <c r="C1307">
+        <v>2</v>
+      </c>
+      <c r="D1307">
+        <v>0.62</v>
+      </c>
+      <c r="E1307" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1308" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1308">
+        <v>2.4</v>
+      </c>
+      <c r="C1308">
+        <v>1</v>
+      </c>
+      <c r="D1308">
+        <v>2.4</v>
+      </c>
+      <c r="E1308" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1309" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1309">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C1309">
+        <v>1</v>
+      </c>
+      <c r="D1309">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="E1309" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1310" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1310">
+        <v>2</v>
+      </c>
+      <c r="C1310">
+        <v>1</v>
+      </c>
+      <c r="D1310">
+        <v>2</v>
+      </c>
+      <c r="E1310" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1311" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1311">
+        <v>4.5</v>
+      </c>
+      <c r="C1311">
+        <v>1</v>
+      </c>
+      <c r="D1311">
+        <v>4.5</v>
+      </c>
+      <c r="E1311" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1312" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1312">
+        <v>3</v>
+      </c>
+      <c r="C1312">
+        <v>1</v>
+      </c>
+      <c r="D1312">
+        <v>3</v>
+      </c>
+      <c r="E1312" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1313" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1313">
+        <v>9</v>
+      </c>
+      <c r="C1313">
+        <v>3</v>
+      </c>
+      <c r="D1313">
+        <v>27</v>
+      </c>
+      <c r="E1313" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1314" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1314">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="C1314">
+        <v>1</v>
+      </c>
+      <c r="D1314">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="E1314" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1315" t="s">
+        <v>363</v>
+      </c>
+      <c r="B1315">
+        <v>17.5</v>
+      </c>
+      <c r="C1315">
+        <v>2</v>
+      </c>
+      <c r="D1315">
+        <v>35</v>
+      </c>
+      <c r="E1315" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1316" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1316">
+        <v>11</v>
+      </c>
+      <c r="C1316">
+        <v>1</v>
+      </c>
+      <c r="D1316">
+        <v>11</v>
+      </c>
+      <c r="E1316" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1317" t="s">
+        <v>412</v>
+      </c>
+      <c r="B1317">
+        <v>19</v>
+      </c>
+      <c r="C1317">
+        <v>0.5</v>
+      </c>
+      <c r="D1317">
+        <v>9.5</v>
+      </c>
+      <c r="E1317" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1318" t="s">
+        <v>413</v>
+      </c>
+      <c r="B1318">
+        <v>3</v>
+      </c>
+      <c r="C1318">
+        <v>2</v>
+      </c>
+      <c r="D1318">
+        <v>6</v>
+      </c>
+      <c r="E1318" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1319" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1319">
+        <v>7.5</v>
+      </c>
+      <c r="C1319">
+        <v>1</v>
+      </c>
+      <c r="D1319">
+        <v>7.5</v>
+      </c>
+      <c r="E1319" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1320" t="s">
+        <v>414</v>
+      </c>
+      <c r="B1320">
+        <v>3.5</v>
+      </c>
+      <c r="C1320">
+        <v>1</v>
+      </c>
+      <c r="D1320">
+        <v>3.5</v>
+      </c>
+      <c r="E1320" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1321" t="s">
+        <v>415</v>
+      </c>
+      <c r="B1321">
+        <v>3.5</v>
+      </c>
+      <c r="C1321">
+        <v>2</v>
+      </c>
+      <c r="D1321">
+        <v>7</v>
+      </c>
+      <c r="E1321" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1322" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1322">
+        <v>3.8</v>
+      </c>
+      <c r="C1322">
+        <v>2</v>
+      </c>
+      <c r="D1322">
+        <v>7.6</v>
+      </c>
+      <c r="E1322" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1323" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1323">
+        <v>3.2</v>
+      </c>
+      <c r="C1323">
+        <v>1</v>
+      </c>
+      <c r="D1323">
+        <v>3.2</v>
+      </c>
+      <c r="E1323" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1324" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1324">
+        <v>2.48</v>
+      </c>
+      <c r="C1324">
+        <v>1</v>
+      </c>
+      <c r="D1324">
+        <v>2.48</v>
+      </c>
+      <c r="E1324" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1325" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1325">
+        <v>0.88</v>
+      </c>
+      <c r="C1325">
+        <v>5</v>
+      </c>
+      <c r="D1325">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E1325" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1326" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1326">
+        <v>4</v>
+      </c>
+      <c r="C1326">
+        <v>1</v>
+      </c>
+      <c r="D1326">
+        <v>4</v>
+      </c>
+      <c r="E1326" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1327" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1327">
+        <v>1.7</v>
+      </c>
+      <c r="C1327">
+        <v>1</v>
+      </c>
+      <c r="D1327">
+        <v>1.7</v>
+      </c>
+      <c r="E1327" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1328" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1328">
+        <v>1.42</v>
+      </c>
+      <c r="C1328">
+        <v>1</v>
+      </c>
+      <c r="D1328">
+        <v>1.42</v>
+      </c>
+      <c r="E1328" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1329" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1329">
+        <v>1.68</v>
+      </c>
+      <c r="C1329">
+        <v>1</v>
+      </c>
+      <c r="D1329">
+        <v>1.68</v>
+      </c>
+      <c r="E1329" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1330" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1330">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C1330">
+        <v>3</v>
+      </c>
+      <c r="D1330">
+        <v>3.33</v>
+      </c>
+      <c r="E1330" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1331" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1331">
+        <v>5.5</v>
+      </c>
+      <c r="C1331">
+        <v>1</v>
+      </c>
+      <c r="D1331">
+        <v>5.5</v>
+      </c>
+      <c r="E1331" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1332" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1332">
+        <v>3.9</v>
+      </c>
+      <c r="C1332">
+        <v>1</v>
+      </c>
+      <c r="D1332">
+        <v>3.9</v>
+      </c>
+      <c r="E1332" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1333" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1333">
+        <v>3.5</v>
+      </c>
+      <c r="C1333">
+        <v>1</v>
+      </c>
+      <c r="D1333">
+        <v>3.5</v>
+      </c>
+      <c r="E1333" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1334" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1334">
+        <v>2.5</v>
+      </c>
+      <c r="C1334">
+        <v>1</v>
+      </c>
+      <c r="D1334">
+        <v>2.5</v>
+      </c>
+      <c r="E1334" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1335" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1335">
+        <v>5</v>
+      </c>
+      <c r="C1335">
+        <v>0.45</v>
+      </c>
+      <c r="D1335">
+        <v>2.25</v>
+      </c>
+      <c r="E1335" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1336" t="s">
+        <v>354</v>
+      </c>
+      <c r="B1336">
+        <v>11</v>
+      </c>
+      <c r="C1336">
+        <v>1.2</v>
+      </c>
+      <c r="D1336">
+        <v>13.2</v>
+      </c>
+      <c r="E1336" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1337" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1337">
+        <v>27</v>
+      </c>
+      <c r="C1337">
+        <v>0.2</v>
+      </c>
+      <c r="D1337">
+        <v>5.4</v>
+      </c>
+      <c r="E1337" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1338" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1338">
+        <v>8.5</v>
+      </c>
+      <c r="C1338">
+        <v>1</v>
+      </c>
+      <c r="D1338">
+        <v>8.5</v>
+      </c>
+      <c r="E1338" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1339" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1339">
+        <v>3.3</v>
+      </c>
+      <c r="C1339">
+        <v>2</v>
+      </c>
+      <c r="D1339">
+        <v>6.6</v>
+      </c>
+      <c r="E1339" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1340" t="s">
+        <v>379</v>
+      </c>
+      <c r="B1340">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C1340">
+        <v>2</v>
+      </c>
+      <c r="D1340">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E1340" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1341" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1341">
+        <v>6.5</v>
+      </c>
+      <c r="C1341">
+        <v>1</v>
+      </c>
+      <c r="D1341">
+        <v>6.5</v>
+      </c>
+      <c r="E1341" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1342" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1342">
+        <v>5.25</v>
+      </c>
+      <c r="C1342">
+        <v>1</v>
+      </c>
+      <c r="D1342">
+        <v>5.25</v>
+      </c>
+      <c r="E1342" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1343" t="s">
+        <v>417</v>
+      </c>
+      <c r="B1343">
+        <v>13</v>
+      </c>
+      <c r="C1343">
+        <v>1</v>
+      </c>
+      <c r="D1343">
+        <v>13</v>
+      </c>
+      <c r="E1343" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1344" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1344">
+        <v>6</v>
+      </c>
+      <c r="C1344">
+        <v>1</v>
+      </c>
+      <c r="D1344">
+        <v>6</v>
+      </c>
+      <c r="E1344" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1345" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1345">
+        <v>4</v>
+      </c>
+      <c r="C1345">
+        <v>1</v>
+      </c>
+      <c r="D1345">
+        <v>4</v>
+      </c>
+      <c r="E1345" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1346" t="s">
+        <v>418</v>
+      </c>
+      <c r="B1346">
+        <v>5</v>
+      </c>
+      <c r="C1346">
+        <v>1</v>
+      </c>
+      <c r="D1346">
+        <v>5</v>
+      </c>
+      <c r="E1346" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1347" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1347">
+        <v>3.8</v>
+      </c>
+      <c r="C1347">
+        <v>1</v>
+      </c>
+      <c r="D1347">
+        <v>3.8</v>
+      </c>
+      <c r="E1347" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1348" t="s">
+        <v>419</v>
+      </c>
+      <c r="B1348">
+        <v>4.75</v>
+      </c>
+      <c r="C1348">
+        <v>1</v>
+      </c>
+      <c r="D1348">
+        <v>4.75</v>
+      </c>
+      <c r="E1348" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1349" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1349">
+        <v>6.9</v>
+      </c>
+      <c r="C1349">
+        <v>0.25</v>
+      </c>
+      <c r="D1349">
+        <v>1.73</v>
+      </c>
+      <c r="E1349" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1350" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1350">
+        <v>0.91</v>
+      </c>
+      <c r="C1350">
+        <v>3</v>
+      </c>
+      <c r="D1350">
+        <v>2.73</v>
+      </c>
+      <c r="E1350" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1351" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1351">
+        <v>1.95</v>
+      </c>
+      <c r="C1351">
+        <v>1</v>
+      </c>
+      <c r="D1351">
+        <v>1.95</v>
+      </c>
+      <c r="E1351" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1352" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1352">
+        <v>0.88</v>
+      </c>
+      <c r="C1352">
+        <v>4</v>
+      </c>
+      <c r="D1352">
+        <v>3.52</v>
+      </c>
+      <c r="E1352" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1353" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1353">
+        <v>11.5</v>
+      </c>
+      <c r="C1353">
+        <v>0.8</v>
+      </c>
+      <c r="D1353">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E1353" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1354" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1354">
+        <v>2.23</v>
+      </c>
+      <c r="C1354">
+        <v>1</v>
+      </c>
+      <c r="D1354">
+        <v>2.23</v>
+      </c>
+      <c r="E1354" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1355" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1355">
+        <v>1.96</v>
+      </c>
+      <c r="C1355">
+        <v>1</v>
+      </c>
+      <c r="D1355">
+        <v>1.96</v>
+      </c>
+      <c r="E1355" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1356" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1356">
+        <v>6.3</v>
+      </c>
+      <c r="C1356">
+        <v>1</v>
+      </c>
+      <c r="D1356">
+        <v>6.3</v>
+      </c>
+      <c r="E1356" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1357" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1357">
+        <v>3.5</v>
+      </c>
+      <c r="C1357">
+        <v>1</v>
+      </c>
+      <c r="D1357">
+        <v>3.5</v>
+      </c>
+      <c r="E1357" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1358" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1358">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="C1358">
+        <v>5</v>
+      </c>
+      <c r="D1358">
+        <v>5.55</v>
+      </c>
+      <c r="E1358" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1359" t="s">
+        <v>360</v>
+      </c>
+      <c r="B1359">
+        <v>2.23</v>
+      </c>
+      <c r="C1359">
+        <v>1</v>
+      </c>
+      <c r="D1359">
+        <v>2.23</v>
+      </c>
+      <c r="E1359" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1360" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1360">
+        <v>2</v>
+      </c>
+      <c r="C1360">
+        <v>1</v>
+      </c>
+      <c r="D1360">
+        <v>2</v>
+      </c>
+      <c r="E1360" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1361" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1361">
+        <v>3.9</v>
+      </c>
+      <c r="C1361">
+        <v>1</v>
+      </c>
+      <c r="D1361">
+        <v>3.9</v>
+      </c>
+      <c r="E1361" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1362" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1362">
+        <v>3.5</v>
+      </c>
+      <c r="C1362">
+        <v>1</v>
+      </c>
+      <c r="D1362">
+        <v>3.5</v>
+      </c>
+      <c r="E1362" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1363" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1363">
+        <v>2.5</v>
+      </c>
+      <c r="C1363">
+        <v>1</v>
+      </c>
+      <c r="D1363">
+        <v>2.5</v>
+      </c>
+      <c r="E1363" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1364" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1364">
+        <v>16</v>
+      </c>
+      <c r="C1364">
+        <v>3</v>
+      </c>
+      <c r="D1364">
+        <v>48</v>
+      </c>
+      <c r="E1364" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1365" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1365">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="C1365">
+        <v>1</v>
+      </c>
+      <c r="D1365">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="E1365" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1366" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1366">
+        <v>5</v>
+      </c>
+      <c r="C1366">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D1366">
+        <v>2.75</v>
+      </c>
+      <c r="E1366" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1367" t="s">
+        <v>420</v>
+      </c>
+      <c r="B1367">
+        <v>1.95</v>
+      </c>
+      <c r="C1367">
+        <v>1</v>
+      </c>
+      <c r="D1367">
+        <v>1.95</v>
+      </c>
+      <c r="E1367" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1368" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1368">
+        <v>14.5</v>
+      </c>
+      <c r="C1368">
+        <v>1</v>
+      </c>
+      <c r="D1368">
+        <v>14.5</v>
+      </c>
+      <c r="E1368" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1369" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1369">
+        <v>5</v>
+      </c>
+      <c r="C1369">
+        <v>1</v>
+      </c>
+      <c r="D1369">
+        <v>5</v>
+      </c>
+      <c r="E1369" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1370" t="s">
+        <v>421</v>
+      </c>
+      <c r="B1370">
+        <v>1.7</v>
+      </c>
+      <c r="C1370">
+        <v>3</v>
+      </c>
+      <c r="D1370">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E1370" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1371" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1371">
+        <v>1</v>
+      </c>
+      <c r="C1371">
+        <v>2</v>
+      </c>
+      <c r="D1371">
+        <v>2</v>
+      </c>
+      <c r="E1371" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1372" t="s">
+        <v>422</v>
+      </c>
+      <c r="B1372">
+        <v>5.5</v>
+      </c>
+      <c r="C1372">
+        <v>1</v>
+      </c>
+      <c r="D1372">
+        <v>5.5</v>
+      </c>
+      <c r="E1372" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1373" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1373">
+        <v>6.5</v>
+      </c>
+      <c r="C1373">
+        <v>1</v>
+      </c>
+      <c r="D1373">
+        <v>6.5</v>
+      </c>
+      <c r="E1373" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1374" t="s">
+        <v>423</v>
+      </c>
+      <c r="B1374">
+        <v>1.65</v>
+      </c>
+      <c r="C1374">
+        <v>1</v>
+      </c>
+      <c r="D1374">
+        <v>1.65</v>
+      </c>
+      <c r="E1374" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1375" t="s">
+        <v>328</v>
+      </c>
+      <c r="B1375">
+        <v>5.2</v>
+      </c>
+      <c r="C1375">
+        <v>1</v>
+      </c>
+      <c r="D1375">
+        <v>5.2</v>
+      </c>
+      <c r="E1375" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1376" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1376">
+        <v>6.9</v>
+      </c>
+      <c r="C1376">
+        <v>0.25</v>
+      </c>
+      <c r="D1376">
+        <v>1.73</v>
+      </c>
+      <c r="E1376" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1377" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1377">
+        <v>0.91</v>
+      </c>
+      <c r="C1377">
+        <v>2</v>
+      </c>
+      <c r="D1377">
+        <v>1.82</v>
+      </c>
+      <c r="E1377" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1378" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1378">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1378">
+        <v>2</v>
+      </c>
+      <c r="D1378">
+        <v>3.5</v>
+      </c>
+      <c r="E1378" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1379" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1379">
+        <v>1.95</v>
+      </c>
+      <c r="C1379">
+        <v>1</v>
+      </c>
+      <c r="D1379">
+        <v>1.95</v>
+      </c>
+      <c r="E1379" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1380" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1380">
+        <v>1.24</v>
+      </c>
+      <c r="C1380">
+        <v>4</v>
+      </c>
+      <c r="D1380">
+        <v>4.96</v>
+      </c>
+      <c r="E1380" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1381" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1381">
+        <v>11.5</v>
+      </c>
+      <c r="C1381">
+        <v>0.35</v>
+      </c>
+      <c r="D1381">
+        <v>4.03</v>
+      </c>
+      <c r="E1381" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1382" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1382">
+        <v>1.68</v>
+      </c>
+      <c r="C1382">
+        <v>1</v>
+      </c>
+      <c r="D1382">
+        <v>1.68</v>
+      </c>
+      <c r="E1382" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1383" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1383">
+        <v>0.47</v>
+      </c>
+      <c r="C1383">
+        <v>2</v>
+      </c>
+      <c r="D1383">
+        <v>0.94</v>
+      </c>
+      <c r="E1383" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1384" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1384">
+        <v>3.4</v>
+      </c>
+      <c r="C1384">
+        <v>1</v>
+      </c>
+      <c r="D1384">
+        <v>3.4</v>
+      </c>
+      <c r="E1384" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1385" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1385">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C1385">
+        <v>6</v>
+      </c>
+      <c r="D1385">
+        <v>3.3</v>
+      </c>
+      <c r="E1385" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1386" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1386">
+        <v>4.05</v>
+      </c>
+      <c r="C1386">
+        <v>1</v>
+      </c>
+      <c r="D1386">
+        <v>4.05</v>
+      </c>
+      <c r="E1386" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1387" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1387">
+        <v>4</v>
+      </c>
+      <c r="C1387">
+        <v>1</v>
+      </c>
+      <c r="D1387">
+        <v>4</v>
+      </c>
+      <c r="E1387" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1388" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1388">
+        <v>2.9</v>
+      </c>
+      <c r="C1388">
+        <v>1</v>
+      </c>
+      <c r="D1388">
+        <v>2.9</v>
+      </c>
+      <c r="E1388" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1389" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1389">
+        <v>3.2</v>
+      </c>
+      <c r="C1389">
+        <v>1</v>
+      </c>
+      <c r="D1389">
+        <v>3.2</v>
+      </c>
+      <c r="E1389" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1390" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1390">
+        <v>2.5</v>
+      </c>
+      <c r="C1390">
+        <v>2</v>
+      </c>
+      <c r="D1390">
+        <v>5</v>
+      </c>
+      <c r="E1390" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1391" t="s">
+        <v>362</v>
+      </c>
+      <c r="B1391">
+        <v>16</v>
+      </c>
+      <c r="C1391">
+        <v>1</v>
+      </c>
+      <c r="D1391">
+        <v>16</v>
+      </c>
+      <c r="E1391" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1392" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1392">
+        <v>15.68</v>
+      </c>
+      <c r="C1392">
+        <v>1</v>
+      </c>
+      <c r="D1392">
+        <v>15.68</v>
+      </c>
+      <c r="E1392" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1393" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1393">
+        <v>4.3</v>
+      </c>
+      <c r="C1393">
+        <v>0.6</v>
+      </c>
+      <c r="D1393">
+        <v>2.58</v>
+      </c>
+      <c r="E1393" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1394" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1394">
+        <v>34</v>
+      </c>
+      <c r="C1394">
+        <v>0.8</v>
+      </c>
+      <c r="D1394">
+        <v>27.2</v>
+      </c>
+      <c r="E1394" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1395" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1395">
+        <v>27</v>
+      </c>
+      <c r="C1395">
+        <v>0.2</v>
+      </c>
+      <c r="D1395">
+        <v>5.4</v>
+      </c>
+      <c r="E1395" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1396" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1396">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C1396">
+        <v>2</v>
+      </c>
+      <c r="D1396">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E1396" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1397" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1397">
+        <v>7.7</v>
+      </c>
+      <c r="C1397">
+        <v>2</v>
+      </c>
+      <c r="D1397">
+        <v>15.4</v>
+      </c>
+      <c r="E1397" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1398" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1398">
+        <v>10.9</v>
+      </c>
+      <c r="C1398">
+        <v>1</v>
+      </c>
+      <c r="D1398">
+        <v>10.9</v>
+      </c>
+      <c r="E1398" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1399" t="s">
+        <v>426</v>
+      </c>
+      <c r="B1399">
+        <v>2</v>
+      </c>
+      <c r="C1399">
+        <v>1</v>
+      </c>
+      <c r="D1399">
+        <v>2</v>
+      </c>
+      <c r="E1399" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1400" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1400">
+        <v>2.75</v>
+      </c>
+      <c r="C1400">
+        <v>3</v>
+      </c>
+      <c r="D1400">
+        <v>8.25</v>
+      </c>
+      <c r="E1400" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1401" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1401">
+        <v>3.5</v>
+      </c>
+      <c r="C1401">
+        <v>2</v>
+      </c>
+      <c r="D1401">
+        <v>7</v>
+      </c>
+      <c r="E1401" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1402" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1402">
+        <v>8.5</v>
+      </c>
+      <c r="C1402">
+        <v>2</v>
+      </c>
+      <c r="D1402">
+        <v>17</v>
+      </c>
+      <c r="E1402" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1403" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1403">
+        <v>5</v>
+      </c>
+      <c r="C1403">
+        <v>2</v>
+      </c>
+      <c r="D1403">
+        <v>10</v>
+      </c>
+      <c r="E1403" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1404" t="s">
+        <v>364</v>
+      </c>
+      <c r="B1404">
+        <v>2.8</v>
+      </c>
+      <c r="C1404">
+        <v>2</v>
+      </c>
+      <c r="D1404">
+        <v>5.6</v>
+      </c>
+      <c r="E1404" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1405" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1405">
+        <v>2.8</v>
+      </c>
+      <c r="C1405">
+        <v>2</v>
+      </c>
+      <c r="D1405">
+        <v>5.6</v>
+      </c>
+      <c r="E1405" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1406" t="s">
+        <v>393</v>
+      </c>
+      <c r="B1406">
+        <v>2.8</v>
+      </c>
+      <c r="C1406">
+        <v>1</v>
+      </c>
+      <c r="D1406">
+        <v>2.8</v>
+      </c>
+      <c r="E1406" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1407" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1407">
+        <v>3.7</v>
+      </c>
+      <c r="C1407">
+        <v>1</v>
+      </c>
+      <c r="D1407">
+        <v>3.7</v>
+      </c>
+      <c r="E1407" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1408" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1408">
+        <v>3.7</v>
+      </c>
+      <c r="C1408">
+        <v>1</v>
+      </c>
+      <c r="D1408">
+        <v>3.7</v>
+      </c>
+      <c r="E1408" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1409" t="s">
+        <v>406</v>
+      </c>
+      <c r="B1409">
+        <v>4</v>
+      </c>
+      <c r="C1409">
+        <v>1</v>
+      </c>
+      <c r="D1409">
+        <v>4</v>
+      </c>
+      <c r="E1409" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1410" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1410">
+        <v>5</v>
+      </c>
+      <c r="C1410">
+        <v>1</v>
+      </c>
+      <c r="D1410">
+        <v>5</v>
+      </c>
+      <c r="E1410" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1411" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1411">
+        <v>8.5</v>
+      </c>
+      <c r="C1411">
+        <v>2</v>
+      </c>
+      <c r="D1411">
+        <v>17</v>
+      </c>
+      <c r="E1411" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1412" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1412">
+        <v>5.5</v>
+      </c>
+      <c r="C1412">
+        <v>2</v>
+      </c>
+      <c r="D1412">
+        <v>11</v>
+      </c>
+      <c r="E1412" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1413" t="s">
+        <v>325</v>
+      </c>
+      <c r="B1413">
+        <v>15</v>
+      </c>
+      <c r="C1413">
+        <v>3</v>
+      </c>
+      <c r="D1413">
+        <v>45</v>
+      </c>
+      <c r="E1413" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1414" t="s">
+        <v>428</v>
+      </c>
+      <c r="B1414">
+        <v>2</v>
+      </c>
+      <c r="C1414">
+        <v>1</v>
+      </c>
+      <c r="D1414">
+        <v>1.75</v>
+      </c>
+      <c r="E1414" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1415" t="s">
+        <v>429</v>
+      </c>
+      <c r="B1415">
+        <v>2</v>
+      </c>
+      <c r="C1415">
+        <v>1</v>
+      </c>
+      <c r="D1415">
+        <v>1.75</v>
+      </c>
+      <c r="E1415" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1416" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1416">
+        <v>9</v>
+      </c>
+      <c r="C1416">
+        <v>1</v>
+      </c>
+      <c r="D1416">
+        <v>9</v>
+      </c>
+      <c r="E1416" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1417" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1417">
+        <v>11</v>
+      </c>
+      <c r="C1417">
+        <v>1</v>
+      </c>
+      <c r="D1417">
+        <v>11</v>
+      </c>
+      <c r="E1417" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1418" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1418">
+        <v>4</v>
+      </c>
+      <c r="C1418">
+        <v>2</v>
+      </c>
+      <c r="D1418">
+        <v>8</v>
+      </c>
+      <c r="E1418" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1419" t="s">
+        <v>423</v>
+      </c>
+      <c r="B1419">
+        <v>1.65</v>
+      </c>
+      <c r="C1419">
+        <v>1</v>
+      </c>
+      <c r="D1419">
+        <v>1.65</v>
+      </c>
+      <c r="E1419" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1420" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1420">
+        <v>8</v>
+      </c>
+      <c r="C1420">
+        <v>2</v>
+      </c>
+      <c r="D1420">
+        <v>16</v>
+      </c>
+      <c r="E1420" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1421" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1421">
+        <v>3</v>
+      </c>
+      <c r="C1421">
+        <v>3</v>
+      </c>
+      <c r="D1421">
+        <v>9</v>
+      </c>
+      <c r="E1421" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1422" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1422">
+        <v>3</v>
+      </c>
+      <c r="C1422">
+        <v>1</v>
+      </c>
+      <c r="D1422">
+        <v>3</v>
+      </c>
+      <c r="E1422" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1423" t="s">
+        <v>431</v>
+      </c>
+      <c r="B1423">
+        <v>10</v>
+      </c>
+      <c r="C1423">
+        <v>1</v>
+      </c>
+      <c r="D1423">
+        <v>10</v>
+      </c>
+      <c r="E1423" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1424" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1424">
+        <v>4.5</v>
+      </c>
+      <c r="C1424">
+        <v>1</v>
+      </c>
+      <c r="D1424">
+        <v>4.5</v>
+      </c>
+      <c r="E1424" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1425" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1425">
+        <v>2.48</v>
+      </c>
+      <c r="C1425">
+        <v>1</v>
+      </c>
+      <c r="D1425">
+        <v>2.48</v>
+      </c>
+      <c r="E1425" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1426" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1426">
+        <v>0.46</v>
+      </c>
+      <c r="C1426">
+        <v>5</v>
+      </c>
+      <c r="D1426">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E1426" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1427" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1427">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1427">
+        <v>4</v>
+      </c>
+      <c r="D1427">
+        <v>8</v>
+      </c>
+      <c r="E1427" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1428" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1428">
+        <v>3.9</v>
+      </c>
+      <c r="C1428">
+        <v>1</v>
+      </c>
+      <c r="D1428">
+        <v>3.9</v>
+      </c>
+      <c r="E1428" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1429" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1429">
+        <v>1.42</v>
+      </c>
+      <c r="C1429">
+        <v>3</v>
+      </c>
+      <c r="D1429">
+        <v>4.26</v>
+      </c>
+      <c r="E1429" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1430" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1430">
+        <v>3</v>
+      </c>
+      <c r="C1430">
+        <v>1</v>
+      </c>
+      <c r="D1430">
+        <v>3</v>
+      </c>
+      <c r="E1430" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1431" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1431">
+        <v>1.56</v>
+      </c>
+      <c r="C1431">
+        <v>1</v>
+      </c>
+      <c r="D1431">
+        <v>1.56</v>
+      </c>
+      <c r="E1431" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1432" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1432">
+        <v>2.4</v>
+      </c>
+      <c r="C1432">
+        <v>1</v>
+      </c>
+      <c r="D1432">
+        <v>2.4</v>
+      </c>
+      <c r="E1432" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1433" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1433">
+        <v>3.5</v>
+      </c>
+      <c r="C1433">
+        <v>1</v>
+      </c>
+      <c r="D1433">
+        <v>3.5</v>
+      </c>
+      <c r="E1433" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1434" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1434">
+        <v>0.97</v>
+      </c>
+      <c r="C1434">
+        <v>6</v>
+      </c>
+      <c r="D1434">
+        <v>5.82</v>
+      </c>
+      <c r="E1434" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1435" t="s">
+        <v>432</v>
+      </c>
+      <c r="B1435">
+        <v>3.9</v>
+      </c>
+      <c r="C1435">
+        <v>1</v>
+      </c>
+      <c r="D1435">
+        <v>3.9</v>
+      </c>
+      <c r="E1435" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1436" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1436">
+        <v>3</v>
+      </c>
+      <c r="C1436">
+        <v>1</v>
+      </c>
+      <c r="D1436">
+        <v>3</v>
+      </c>
+      <c r="E1436" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1437" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1437">
+        <v>3.9</v>
+      </c>
+      <c r="C1437">
+        <v>1</v>
+      </c>
+      <c r="D1437">
+        <v>3.9</v>
+      </c>
+      <c r="E1437" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1438" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1438">
+        <v>3.5</v>
+      </c>
+      <c r="C1438">
+        <v>1</v>
+      </c>
+      <c r="D1438">
+        <v>3.5</v>
+      </c>
+      <c r="E1438" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1439" t="s">
+        <v>339</v>
+      </c>
+      <c r="B1439">
+        <v>3.2</v>
+      </c>
+      <c r="C1439">
+        <v>1</v>
+      </c>
+      <c r="D1439">
+        <v>3.2</v>
+      </c>
+      <c r="E1439" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1440" t="s">
+        <v>433</v>
+      </c>
+      <c r="B1440">
+        <v>2.1</v>
+      </c>
+      <c r="C1440">
+        <v>1</v>
+      </c>
+      <c r="D1440">
+        <v>2.1</v>
+      </c>
+      <c r="E1440" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1441" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1441">
+        <v>2.5</v>
+      </c>
+      <c r="C1441">
+        <v>1</v>
+      </c>
+      <c r="D1441">
+        <v>2.5</v>
+      </c>
+      <c r="E1441" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1442" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1442">
+        <v>12.5</v>
+      </c>
+      <c r="C1442">
+        <v>1</v>
+      </c>
+      <c r="D1442">
+        <v>12.5</v>
+      </c>
+      <c r="E1442" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1443" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1443">
+        <v>4.5</v>
+      </c>
+      <c r="C1443">
+        <v>2</v>
+      </c>
+      <c r="D1443">
+        <v>9</v>
+      </c>
+      <c r="E1443" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1444" t="s">
+        <v>434</v>
+      </c>
+      <c r="B1444">
+        <v>3.3</v>
+      </c>
+      <c r="C1444">
+        <v>1</v>
+      </c>
+      <c r="D1444">
+        <v>3.3</v>
+      </c>
+      <c r="E1444" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1445" t="s">
+        <v>435</v>
+      </c>
+      <c r="B1445">
+        <v>4</v>
+      </c>
+      <c r="C1445">
+        <v>1</v>
+      </c>
+      <c r="D1445">
+        <v>4</v>
+      </c>
+      <c r="E1445" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1446" t="s">
+        <v>404</v>
+      </c>
+      <c r="B1446">
+        <v>1.75</v>
+      </c>
+      <c r="C1446">
+        <v>3</v>
+      </c>
+      <c r="D1446">
+        <v>5.25</v>
+      </c>
+      <c r="E1446" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1447" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1447">
+        <v>3.05</v>
+      </c>
+      <c r="C1447">
+        <v>1</v>
+      </c>
+      <c r="D1447">
+        <v>3.05</v>
+      </c>
+      <c r="E1447" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1448" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1448">
+        <v>15.2</v>
+      </c>
+      <c r="C1448">
+        <v>2</v>
+      </c>
+      <c r="D1448">
+        <v>30.4</v>
+      </c>
+      <c r="E1448" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1449" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1449">
+        <v>19</v>
+      </c>
+      <c r="C1449">
+        <v>1</v>
+      </c>
+      <c r="D1449">
+        <v>19</v>
+      </c>
+      <c r="E1449" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1450" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1450">
+        <v>7.15</v>
+      </c>
+      <c r="C1450">
+        <v>2</v>
+      </c>
+      <c r="D1450">
+        <v>14.3</v>
+      </c>
+      <c r="E1450" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1451" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1451">
+        <v>2.8</v>
+      </c>
+      <c r="C1451">
+        <v>2</v>
+      </c>
+      <c r="D1451">
+        <v>5.6</v>
+      </c>
+      <c r="E1451" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1452" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1452">
+        <v>2.5</v>
+      </c>
+      <c r="C1452">
+        <v>1</v>
+      </c>
+      <c r="D1452">
+        <v>2.5</v>
+      </c>
+      <c r="E1452" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1453" t="s">
+        <v>351</v>
+      </c>
+      <c r="B1453">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C1453">
+        <v>2</v>
+      </c>
+      <c r="D1453">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E1453" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1454" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1454">
+        <v>4</v>
+      </c>
+      <c r="C1454">
+        <v>1</v>
+      </c>
+      <c r="D1454">
+        <v>4</v>
+      </c>
+      <c r="E1454" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1455" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1455">
+        <v>30</v>
+      </c>
+      <c r="C1455">
+        <v>0.2</v>
+      </c>
+      <c r="D1455">
+        <v>6</v>
+      </c>
+      <c r="E1455" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1456" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1456">
+        <v>5.3</v>
+      </c>
+      <c r="C1456">
+        <v>1</v>
+      </c>
+      <c r="D1456">
+        <v>5.3</v>
+      </c>
+      <c r="E1456" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1457" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1457">
+        <v>5.5</v>
+      </c>
+      <c r="C1457">
+        <v>2</v>
+      </c>
+      <c r="D1457">
+        <v>11</v>
+      </c>
+      <c r="E1457" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1458" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1458">
+        <v>6</v>
+      </c>
+      <c r="C1458">
+        <v>3</v>
+      </c>
+      <c r="D1458">
+        <v>18</v>
+      </c>
+      <c r="E1458" s="1">
+        <v>46056</v>
       </c>
     </row>
   </sheetData>
@@ -26477,7 +34396,7 @@
       <c r="A4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>15</v>
       </c>
     </row>
@@ -26485,7 +34404,7 @@
       <c r="A5" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>14</v>
       </c>
     </row>
@@ -26493,7 +34412,7 @@
       <c r="A6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <v>13</v>
       </c>
     </row>
@@ -26501,7 +34420,7 @@
       <c r="A7" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>8</v>
       </c>
     </row>
@@ -26509,7 +34428,7 @@
       <c r="A8" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <v>7</v>
       </c>
     </row>
@@ -26517,7 +34436,7 @@
       <c r="A9" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9">
         <v>5</v>
       </c>
     </row>
@@ -26525,7 +34444,7 @@
       <c r="A10" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10">
         <v>4</v>
       </c>
     </row>
@@ -26533,7 +34452,7 @@
       <c r="A11" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11">
         <v>3</v>
       </c>
     </row>
@@ -26541,7 +34460,7 @@
       <c r="A12" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12">
         <v>2</v>
       </c>
     </row>
@@ -26549,7 +34468,7 @@
       <c r="A13" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13">
         <v>2</v>
       </c>
     </row>
@@ -26557,7 +34476,7 @@
       <c r="A14" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14">
         <v>1</v>
       </c>
     </row>
@@ -26565,7 +34484,7 @@
       <c r="A15" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15">
         <v>74</v>
       </c>
     </row>

--- a/shopping_list.xlsx
+++ b/shopping_list.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1460"/>
+  <dimension ref="A1:E1462"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -25223,9 +25223,43 @@
         <v>2026-05-29</v>
       </c>
     </row>
+    <row r="1461">
+      <c r="A1461" t="str">
+        <v>Washed Potato Bag 4kg</v>
+      </c>
+      <c r="B1461">
+        <v>0</v>
+      </c>
+      <c r="C1461" t="str">
+        <v/>
+      </c>
+      <c r="D1461" t="str">
+        <v/>
+      </c>
+      <c r="E1461" t="str">
+        <v>2026-06-10</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="str">
+        <v>Washed Potato Bag 4kg</v>
+      </c>
+      <c r="B1462">
+        <v>0</v>
+      </c>
+      <c r="C1462" t="str">
+        <v/>
+      </c>
+      <c r="D1462" t="str">
+        <v/>
+      </c>
+      <c r="E1462" t="str">
+        <v>2026-06-11</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1460"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1462"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/shopping_list.xlsx
+++ b/shopping_list.xlsx
@@ -11214,7 +11214,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Woolworths Salmon Tasmanian Atlantic Fillets Skin On</t>
+          <t>Woolworths Fresh Tasmanian Atlantic Skin On Salmon Fillets</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -19042,7 +19042,7 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>Woolworths Salmon Tasmanian Atlantic Fillets Skin On</t>
+          <t>Woolworths Fresh Tasmanian Atlantic Skin On Salmon Fillets</t>
         </is>
       </c>
       <c r="B979" t="n">

--- a/shopping_list.xlsx
+++ b/shopping_list.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1400"/>
+  <dimension ref="A1:E1534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27039,6 +27039,2552 @@
         <is>
           <t>2026-06-11</t>
         </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>Helga's Wholemeal Bread With Grains</t>
+        </is>
+      </c>
+      <c r="B1401" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C1401" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1401" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E1401" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>Smith's Crinkle Cut Potato Chips Multipack Original</t>
+        </is>
+      </c>
+      <c r="B1402" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C1402" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1402" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E1402" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>Woolworths Baby Corn Spears</t>
+        </is>
+      </c>
+      <c r="B1403" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C1403" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1403" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E1403" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>Cadbury Dairy Milk Large Chocolate Block</t>
+        </is>
+      </c>
+      <c r="B1404" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1404" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1404" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1404" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>Lurpak Butter Spreadable</t>
+        </is>
+      </c>
+      <c r="B1405" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C1405" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1405" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E1405" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>Thomas Dux Blue Stilton</t>
+        </is>
+      </c>
+      <c r="B1406" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C1406" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1406" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1406" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>Woolworths Natural Greek Style Yoghurt</t>
+        </is>
+      </c>
+      <c r="B1407" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C1407" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1407" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1407" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>Woolworths Sour Cream</t>
+        </is>
+      </c>
+      <c r="B1408" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C1408" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1408" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E1408" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>Woolworths Full Cream Milk</t>
+        </is>
+      </c>
+      <c r="B1409" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1409" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1409" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>Schweppes Lemon Lime Natural Mineral Water Bottle</t>
+        </is>
+      </c>
+      <c r="B1410" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C1410" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1410" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>Ben &amp; Jerry's Ice Cream Tub Chocolate Chip Cookie Dough</t>
+        </is>
+      </c>
+      <c r="B1411" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1411" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1411" t="n">
+        <v>30</v>
+      </c>
+      <c r="E1411" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>Woolworths Frozen Meat Pies</t>
+        </is>
+      </c>
+      <c r="B1412" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C1412" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1412" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1412" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>Woolworths Ice Cream Cones Boysenberry</t>
+        </is>
+      </c>
+      <c r="B1413" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1413" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1413" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1413" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>Hass Avocado</t>
+        </is>
+      </c>
+      <c r="B1414" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C1414" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1414" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E1414" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>Mushrooms Cups Loose</t>
+        </is>
+      </c>
+      <c r="B1415" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="C1415" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D1415" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="E1415" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>Sweet Potato Gold</t>
+        </is>
+      </c>
+      <c r="B1416" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="C1416" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1416" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E1416" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>The Odd Bunch Lebanese Cucumber Punnet</t>
+        </is>
+      </c>
+      <c r="B1417" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C1417" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1417" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E1417" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>The Odd Bunch Lemon Prepacked</t>
+        </is>
+      </c>
+      <c r="B1418" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C1418" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1418" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E1418" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>Truss Tomatoes</t>
+        </is>
+      </c>
+      <c r="B1419" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="C1419" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1419" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E1419" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>Woolworths Broccolini Bunch</t>
+        </is>
+      </c>
+      <c r="B1420" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C1420" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1420" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>Woolworths Cos Hearts Lettuce</t>
+        </is>
+      </c>
+      <c r="B1421" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C1421" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1421" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>Woolworths Mashing Potatoes Bag</t>
+        </is>
+      </c>
+      <c r="B1422" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1422" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1422" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>Macro Natural Sunflower Kernels</t>
+        </is>
+      </c>
+      <c r="B1423" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1423" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1423" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1423" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>Shine Dishwashing Tablets</t>
+        </is>
+      </c>
+      <c r="B1424" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="C1424" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1424" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E1424" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>Market Value Scotch Fillet</t>
+        </is>
+      </c>
+      <c r="B1425" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="C1425" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1425" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>Woolworths Cook Chicken Roasting Portions Italian Style</t>
+        </is>
+      </c>
+      <c r="B1426" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1426" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1426" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1426" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>Woolworths RSPCA Approved Chicken Breast Fillet</t>
+        </is>
+      </c>
+      <c r="B1427" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="C1427" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1427" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="E1427" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>Strike Paper Towels Embossed 2 Ply</t>
+        </is>
+      </c>
+      <c r="B1428" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C1428" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1428" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E1428" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>Vevelle 2 Ply White Toilet Tissue</t>
+        </is>
+      </c>
+      <c r="B1429" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1429" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1429" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1429" t="n">
+        <v>45568</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>Baby Mum-Mum Snack Vegetable Rice Rusk</t>
+        </is>
+      </c>
+      <c r="B1430" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C1430" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1430" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E1430" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>Home Chef Quiche Lorraine Chilled Meal</t>
+        </is>
+      </c>
+      <c r="B1431" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C1431" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1431" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E1431" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>Helga's Wholemeal Bread With Grains</t>
+        </is>
+      </c>
+      <c r="B1432" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1432" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1432" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1432" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>Woolworths Dreamy Choc Chip Cookies</t>
+        </is>
+      </c>
+      <c r="B1433" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C1433" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1433" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>Pringles Sour Cream &amp; Onion Potato Chips</t>
+        </is>
+      </c>
+      <c r="B1434" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C1434" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1434" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>Sam's Pantry Caramel Brownie Low Sugar Protein Bars</t>
+        </is>
+      </c>
+      <c r="B1435" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C1435" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1435" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>Woolworths Mild Salsa</t>
+        </is>
+      </c>
+      <c r="B1436" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C1436" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1436" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>Arnold's Farm Granola Pink Lady Apple &amp; Cinnamon</t>
+        </is>
+      </c>
+      <c r="B1437" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C1437" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1437" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>Macro Organic Black Bean No Added Salt</t>
+        </is>
+      </c>
+      <c r="B1438" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C1438" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1438" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1438" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>McKenzie's Green Lentil Whole</t>
+        </is>
+      </c>
+      <c r="B1439" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C1439" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1439" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E1439" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>McKenzie's Red Lentils</t>
+        </is>
+      </c>
+      <c r="B1440" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C1440" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1440" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>Woolworths Diced Italian Tomatoes</t>
+        </is>
+      </c>
+      <c r="B1441" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C1441" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1441" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E1441" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>Woolworths 12 Extra Large Free Range Eggs</t>
+        </is>
+      </c>
+      <c r="B1442" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="C1442" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1442" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E1442" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>Essentials White Vinegar</t>
+        </is>
+      </c>
+      <c r="B1443" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C1443" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1443" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E1443" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>Aero Peppermint Milk Chocolate Block</t>
+        </is>
+      </c>
+      <c r="B1444" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1444" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1444" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1444" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>KitKat Milk Chocolate 11 Mini Bars Share Pack</t>
+        </is>
+      </c>
+      <c r="B1445" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C1445" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1445" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E1445" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>Snickers Milk Chocolate Party Share Bag 20 Pieces</t>
+        </is>
+      </c>
+      <c r="B1446" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C1446" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1446" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E1446" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>Mutti Tomato Paste Double Concentrate</t>
+        </is>
+      </c>
+      <c r="B1447" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C1447" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1447" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1447" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>Woolworths Extra Virgin Spanish Olive Oil</t>
+        </is>
+      </c>
+      <c r="B1448" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1448" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1448" t="n">
+        <v>18</v>
+      </c>
+      <c r="E1448" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>Mainland Extra Tasty Cheese Block</t>
+        </is>
+      </c>
+      <c r="B1449" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C1449" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1449" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>Mon Ami French Camembert Cheese</t>
+        </is>
+      </c>
+      <c r="B1450" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C1450" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>Woolworths Full Cream Milk</t>
+        </is>
+      </c>
+      <c r="B1451" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C1451" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1451" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>Schweppes Lemon Lime Bitters Soft Drink Classic Mixers Bottle</t>
+        </is>
+      </c>
+      <c r="B1452" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1452" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1452" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>Ben &amp; Jerry's Ice Cream Tub Chocolate Chip Cookie Dough</t>
+        </is>
+      </c>
+      <c r="B1453" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C1453" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1453" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>Woolworths Frozen Meat Pies</t>
+        </is>
+      </c>
+      <c r="B1454" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C1454" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1454" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>Woolworths Ice Cream Cones Boysenberry</t>
+        </is>
+      </c>
+      <c r="B1455" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C1455" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1455" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>Blueberries Punnet</t>
+        </is>
+      </c>
+      <c r="B1456" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1456" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>Cavendish Bananas</t>
+        </is>
+      </c>
+      <c r="B1457" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>Fresh Broccoli</t>
+        </is>
+      </c>
+      <c r="B1458" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>Fresh Cauliflower Half</t>
+        </is>
+      </c>
+      <c r="B1459" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>Kale Fresh Bunch</t>
+        </is>
+      </c>
+      <c r="B1460" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C1460" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>Lebanese Cucumbers</t>
+        </is>
+      </c>
+      <c r="B1461" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="C1461" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>Strawberries Punnet</t>
+        </is>
+      </c>
+      <c r="B1462" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>Sweet Potato Gold</t>
+        </is>
+      </c>
+      <c r="B1463" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C1463" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1463" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>The Odd Bunch Carrots</t>
+        </is>
+      </c>
+      <c r="B1464" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C1464" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1464" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>The Odd Bunch Lemon Prepacked</t>
+        </is>
+      </c>
+      <c r="B1465" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1465" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>The Odd Bunch Zucchini Prepacked</t>
+        </is>
+      </c>
+      <c r="B1466" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C1466" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>Woolworths Broccolini Bunch</t>
+        </is>
+      </c>
+      <c r="B1467" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1467" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>Woolworths Cherry Tomatoes Punnet</t>
+        </is>
+      </c>
+      <c r="B1468" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C1468" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>Woolworths Corn Sweet</t>
+        </is>
+      </c>
+      <c r="B1469" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C1469" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>Woolworths Cos Hearts Lettuce</t>
+        </is>
+      </c>
+      <c r="B1470" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C1470" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>Woolworths Fresh Continental Parsley Bunch</t>
+        </is>
+      </c>
+      <c r="B1471" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C1471" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1471" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>Woolworths Garlic Heads CLOVE</t>
+        </is>
+      </c>
+      <c r="B1472" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C1472" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1472" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>Woolworths Asparagus Green Bunch</t>
+        </is>
+      </c>
+      <c r="B1473" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C1473" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>Woolworths Red Watermelon Cut Quarter</t>
+        </is>
+      </c>
+      <c r="B1474" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="C1474" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>Macro Natural Sunflower Kernels</t>
+        </is>
+      </c>
+      <c r="B1475" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C1475" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>Macro Organic Natural Pumpkin Kernels</t>
+        </is>
+      </c>
+      <c r="B1476" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1476" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>Ecostore Ultra Sensitive Fragrance Free Laundry Liquid</t>
+        </is>
+      </c>
+      <c r="B1477" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1477" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>Shine Dishwashing Tablets</t>
+        </is>
+      </c>
+      <c r="B1478" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C1478" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>Strike Blue Toilet Cleaner Cistern Blocks</t>
+        </is>
+      </c>
+      <c r="B1479" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1479" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>Katoomba Ingredients Red Lentils</t>
+        </is>
+      </c>
+      <c r="B1480" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1480" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>Woolworths Beef Porterhouse Steak &amp; Butter</t>
+        </is>
+      </c>
+      <c r="B1481" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1481" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>Woolworths RSPCA Approved Chicken Drumsticks</t>
+        </is>
+      </c>
+      <c r="B1482" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C1482" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>Woolworths RSPCA Approved Chicken Thigh Skinless Cutlets Bone-In</t>
+        </is>
+      </c>
+      <c r="B1483" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="C1483" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>Armada Evergreen Garbage Bags Extra Large</t>
+        </is>
+      </c>
+      <c r="B1484" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C1484" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>Strike Paper Towels Embossed 2 Ply</t>
+        </is>
+      </c>
+      <c r="B1485" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C1485" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1485" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>Woolworths Basmati Rice</t>
+        </is>
+      </c>
+      <c r="B1486" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1486" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1486" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>Woolworths Freshwater Basa Fillets Thawed</t>
+        </is>
+      </c>
+      <c r="B1487" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1487" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1487" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>Vevelle 2 Ply White Toilet Tissue</t>
+        </is>
+      </c>
+      <c r="B1488" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1488" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1488" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>Baby Mum-Mum Snack Vegetable Rice Rusk</t>
+        </is>
+      </c>
+      <c r="B1489" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="C1489" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>Home Chef Quiche Spinach &amp; Feta Chilled Meal</t>
+        </is>
+      </c>
+      <c r="B1490" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1490" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1490" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>Helga's Wholemeal Bread With Grains</t>
+        </is>
+      </c>
+      <c r="B1491" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1491" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1491" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>Woolworths Wholegrain Wrap 8Pk</t>
+        </is>
+      </c>
+      <c r="B1492" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C1492" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1492" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>Cadbury Fingers Milk Chocolate Biscuits</t>
+        </is>
+      </c>
+      <c r="B1493" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C1493" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>Woolworths Mild Salsa</t>
+        </is>
+      </c>
+      <c r="B1494" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C1494" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1494" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>Weet-Bix Little Kids Breakfast Cereal</t>
+        </is>
+      </c>
+      <c r="B1495" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1495" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1495" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>Woolworths Diced Italian Tomatoes</t>
+        </is>
+      </c>
+      <c r="B1496" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C1496" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>Woolworths Tuna In Springwater</t>
+        </is>
+      </c>
+      <c r="B1497" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C1497" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>Woolworths 12 Extra Large Free Range Eggs</t>
+        </is>
+      </c>
+      <c r="B1498" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C1498" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>Yumi's Eggplant Mediterranean Dip</t>
+        </is>
+      </c>
+      <c r="B1499" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C1499" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>Hellmann's Real Mayonnaise Squeeze</t>
+        </is>
+      </c>
+      <c r="B1500" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1500" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>Cadbury Dairy Milk Large Top Deck Chocolate Block</t>
+        </is>
+      </c>
+      <c r="B1501" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C1501" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1501" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>KitKat Milk Chocolate Mini Bars Share Pack</t>
+        </is>
+      </c>
+      <c r="B1502" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C1502" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>15</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>Snickers Milk Chocolate Party Share Bag 20 Pieces</t>
+        </is>
+      </c>
+      <c r="B1503" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C1503" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>15</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>Mutti Tomato Paste Double Concentrate</t>
+        </is>
+      </c>
+      <c r="B1504" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C1504" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>Philadelphia Original Cream Cheese Portions Snacks</t>
+        </is>
+      </c>
+      <c r="B1505" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1505" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>Woolworths Full Cream Milk</t>
+        </is>
+      </c>
+      <c r="B1506" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C1506" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>Woolworths Natural Greek Style Yoghurt</t>
+        </is>
+      </c>
+      <c r="B1507" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1507" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>Woolworths Sour Cream</t>
+        </is>
+      </c>
+      <c r="B1508" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C1508" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1508" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>Woolworths 100% Canadian Maple Syrup</t>
+        </is>
+      </c>
+      <c r="B1509" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1509" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1509" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>Schweppes Lemon Lime Bitters Soft Drink Classic Mixers Bottle</t>
+        </is>
+      </c>
+      <c r="B1510" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1510" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1510" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>Woolworths Spring Water Bottles</t>
+        </is>
+      </c>
+      <c r="B1511" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C1511" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1511" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>Woolworths Ice Cream Cones Boysenberry</t>
+        </is>
+      </c>
+      <c r="B1512" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C1512" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1512" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>Beans Round</t>
+        </is>
+      </c>
+      <c r="B1513" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C1513" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D1513" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>Cavendish Bananas</t>
+        </is>
+      </c>
+      <c r="B1514" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="C1514" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1514" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>Hass Avocado</t>
+        </is>
+      </c>
+      <c r="B1515" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C1515" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1515" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>Fresh Broccoli</t>
+        </is>
+      </c>
+      <c r="B1516" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C1516" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1516" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>Fresh Cauliflower Half</t>
+        </is>
+      </c>
+      <c r="B1517" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C1517" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1517" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>Lebanese Cucumbers</t>
+        </is>
+      </c>
+      <c r="B1518" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C1518" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1518" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>The Odd Bunch Capsicum Prepacked</t>
+        </is>
+      </c>
+      <c r="B1519" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C1519" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1519" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>Truss Tomatoes</t>
+        </is>
+      </c>
+      <c r="B1520" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="C1520" t="n">
+        <v>4</v>
+      </c>
+      <c r="D1520" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>Woolworths Cos Hearts Lettuce</t>
+        </is>
+      </c>
+      <c r="B1521" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C1521" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1521" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>Woolworths Garlic Heads CLOVE</t>
+        </is>
+      </c>
+      <c r="B1522" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C1522" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1522" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>Woolworths Green Cabbage Quarter</t>
+        </is>
+      </c>
+      <c r="B1523" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C1523" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1523" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>Woolworths Red Washed Potatoes Bag</t>
+        </is>
+      </c>
+      <c r="B1524" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C1524" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1524" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>Shine Dishwashing Tablets</t>
+        </is>
+      </c>
+      <c r="B1525" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C1525" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1525" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>Strike Blue Toilet Cleaner Cistern Blocks</t>
+        </is>
+      </c>
+      <c r="B1526" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1526" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1526" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1526" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>Old El Paso Fajita Spice Mix Mexican Style</t>
+        </is>
+      </c>
+      <c r="B1527" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1527" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1527" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1527" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>Woolworths 4 Angus Quarter Pound Beef Burgers</t>
+        </is>
+      </c>
+      <c r="B1528" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1528" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1528" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>Woolworths RSPCA Approved Chicken Breast Fillet</t>
+        </is>
+      </c>
+      <c r="B1529" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="C1529" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1529" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>Woolworths RSPCA Approved Chicken Drumsticks</t>
+        </is>
+      </c>
+      <c r="B1530" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C1530" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D1530" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>Armada Evergreen Garbage Bags Extra Large</t>
+        </is>
+      </c>
+      <c r="B1531" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C1531" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1531" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E1531" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>Armada Small Kitchen Tidy Bag</t>
+        </is>
+      </c>
+      <c r="B1532" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1532" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1532" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E1532" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>Strike Paper Towels Embossed 2 Ply</t>
+        </is>
+      </c>
+      <c r="B1533" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C1533" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1533" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E1533" t="n">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>Vevelle 2 Ply White Toilet Tissue</t>
+        </is>
+      </c>
+      <c r="B1534" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1534" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1534" t="n">
+        <v>12</v>
+      </c>
+      <c r="E1534" t="n">
+        <v>45994</v>
       </c>
     </row>
   </sheetData>

--- a/shopping_list.xlsx
+++ b/shopping_list.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1534"/>
+  <dimension ref="A1:E1536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29585,6 +29585,44 @@
       </c>
       <c r="E1534" t="n">
         <v>45994</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>Plum Red</t>
+        </is>
+      </c>
+      <c r="B1535" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="C1535" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1535" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E1535" t="n">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>Woolworths Greek Style Yoghurt</t>
+        </is>
+      </c>
+      <c r="B1536" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1536" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1536" t="n">
+        <v>8</v>
+      </c>
+      <c r="E1536" t="n">
+        <v>45727</v>
       </c>
     </row>
   </sheetData>

--- a/shopping_list.xlsx
+++ b/shopping_list.xlsx
@@ -6635,7 +6635,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Macro Organic Natural Pumpkin Kernels</t>
+          <t>Macro Organic Natural Pumpkin Kernels 250g</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -9618,7 +9618,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Macro Organic Natural Pumpkin Kernels</t>
+          <t>Macro Organic Natural Pumpkin Kernels 250g</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -12069,7 +12069,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Macro Organic Natural Pumpkin Kernels</t>
+          <t>Macro Organic Natural Pumpkin Kernels 250g</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -14482,7 +14482,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>Macro Organic Natural Pumpkin Kernels</t>
+          <t>Macro Organic Natural Pumpkin Kernels 250g</t>
         </is>
       </c>
       <c r="B739" t="n">
@@ -28469,7 +28469,7 @@
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>Macro Organic Natural Pumpkin Kernels</t>
+          <t>Macro Organic Natural Pumpkin Kernels 250g</t>
         </is>
       </c>
       <c r="B1476" t="n">
